--- a/raw/Timetable_2026Autumn_2024DT.xlsx
+++ b/raw/Timetable_2026Autumn_2024DT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30610"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hibiuh-my.sharepoint.com/personal/y20250001_hibiuh_edu_cn/Documents/Academic Affairs Office/Timetable/Timetable_2026Autumn_Shared/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E71E2653-93BD-4866-A470-3DA2B494D579}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0E908FB-6CC9-41CB-B5C4-1BF9DAC25649}"/>
   <bookViews>
-    <workbookView xWindow="1248" yWindow="1980" windowWidth="27096" windowHeight="12120" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1248" yWindow="1980" windowWidth="27096" windowHeight="12120" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2024DT1" sheetId="2" r:id="rId1"/>
@@ -126,7 +126,7 @@
     <t>Safety &amp; Security (SSS)</t>
   </si>
   <si>
-    <t>Leonid Smelov</t>
+    <t>WANG Qilu</t>
   </si>
   <si>
     <t>B404</t>
@@ -1028,7 +1028,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1058,31 +1076,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1121,7 +1115,13 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1471,81 +1471,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="60" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60" t="s">
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60" t="s">
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60" t="s">
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60" t="s">
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="77" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="60" t="s">
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60" t="s">
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60" t="s">
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60" t="s">
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60" t="s">
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="46">
+      <c r="A4" s="51">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1585,7 +1585,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="46"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
@@ -1631,7 +1631,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="46"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
@@ -1693,7 +1693,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="46"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
@@ -1757,7 +1757,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="46"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
@@ -1801,7 +1801,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="46"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
@@ -1845,7 +1845,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="46"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
@@ -1887,7 +1887,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="56">
+      <c r="A11" s="52">
         <v>2</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -1953,7 +1953,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="56"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="14" t="s">
         <v>47</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="56"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="14" t="s">
         <v>50</v>
       </c>
@@ -2077,7 +2077,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="56"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="14" t="s">
         <v>51</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="AA14" s="10"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="56"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="14" t="s">
         <v>52</v>
       </c>
@@ -2163,7 +2163,7 @@
       <c r="AA15" s="10"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="56"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="14" t="s">
         <v>53</v>
       </c>
@@ -2202,7 +2202,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="56"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="14" t="s">
         <v>55</v>
       </c>
@@ -2229,7 +2229,7 @@
       <c r="U17" s="18"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="46">
+      <c r="A18" s="51">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2278,7 +2278,7 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="46"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -2325,7 +2325,7 @@
       <c r="U19" s="6"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="46"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -2372,7 +2372,7 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="46"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
@@ -2419,7 +2419,7 @@
       <c r="U21" s="6"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="46"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="2" t="s">
         <v>60</v>
       </c>
@@ -2466,7 +2466,7 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="46"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="46"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="24" t="s">
         <v>62</v>
       </c>
@@ -2520,7 +2520,7 @@
       <c r="U24" s="28"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="56">
+      <c r="A25" s="52">
         <v>4</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -2569,7 +2569,7 @@
       <c r="U25" s="18"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="56"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="14" t="s">
         <v>64</v>
       </c>
@@ -2616,7 +2616,7 @@
       <c r="U26" s="18"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="56"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="14" t="s">
         <v>65</v>
       </c>
@@ -2663,7 +2663,7 @@
       <c r="U27" s="18"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="56"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="14" t="s">
         <v>66</v>
       </c>
@@ -2710,90 +2710,90 @@
       <c r="U28" s="18"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="56"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="29" t="s">
         <v>67</v>
       </c>
       <c r="C29" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="49"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="55"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="56"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="29" t="s">
         <v>69</v>
       </c>
       <c r="C30" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="50"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="51"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="52"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="58"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="56"/>
+      <c r="A31" s="52"/>
       <c r="B31" s="29" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="53"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="54"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="54"/>
-      <c r="R31" s="54"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="54"/>
-      <c r="U31" s="55"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="46">
+      <c r="A32" s="51">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2842,7 +2842,7 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="46"/>
+      <c r="A33" s="51"/>
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
@@ -2889,7 +2889,7 @@
       <c r="U33" s="6"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="46"/>
+      <c r="A34" s="51"/>
       <c r="B34" s="2" t="s">
         <v>73</v>
       </c>
@@ -2936,117 +2936,117 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="46"/>
+      <c r="A35" s="51"/>
       <c r="B35" s="31" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="48"/>
-      <c r="R35" s="48"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="48"/>
-      <c r="U35" s="49"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="46"/>
+      <c r="A36" s="51"/>
       <c r="B36" s="31" t="s">
         <v>75</v>
       </c>
       <c r="C36" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="50"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="51"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="51"/>
-      <c r="S36" s="51"/>
-      <c r="T36" s="51"/>
-      <c r="U36" s="52"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="57"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="58"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="46"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="31" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="50"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="51"/>
-      <c r="M37" s="51"/>
-      <c r="N37" s="51"/>
-      <c r="O37" s="51"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="51"/>
-      <c r="S37" s="51"/>
-      <c r="T37" s="51"/>
-      <c r="U37" s="52"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="58"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="46"/>
+      <c r="A38" s="51"/>
       <c r="B38" s="31" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="51"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="51"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="51"/>
-      <c r="R38" s="51"/>
-      <c r="S38" s="51"/>
-      <c r="T38" s="51"/>
-      <c r="U38" s="52"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="58"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="56">
+      <c r="A39" s="52">
         <v>6</v>
       </c>
       <c r="B39" s="31" t="s">
@@ -3055,81 +3055,81 @@
       <c r="C39" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="50"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="51"/>
-      <c r="L39" s="51"/>
-      <c r="M39" s="51"/>
-      <c r="N39" s="51"/>
-      <c r="O39" s="51"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="51"/>
-      <c r="R39" s="51"/>
-      <c r="S39" s="51"/>
-      <c r="T39" s="51"/>
-      <c r="U39" s="52"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="58"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="56"/>
+      <c r="A40" s="52"/>
       <c r="B40" s="31" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="50"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="51"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="51"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="51"/>
-      <c r="R40" s="51"/>
-      <c r="S40" s="51"/>
-      <c r="T40" s="51"/>
-      <c r="U40" s="52"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
+      <c r="P40" s="57"/>
+      <c r="Q40" s="57"/>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="58"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="56"/>
+      <c r="A41" s="52"/>
       <c r="B41" s="31" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="53"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="54"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="54"/>
-      <c r="N41" s="54"/>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="54"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="55"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="61"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="56"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="32" t="s">
         <v>81</v>
       </c>
@@ -3176,7 +3176,7 @@
       <c r="U42" s="18"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="56"/>
+      <c r="A43" s="52"/>
       <c r="B43" s="32" t="s">
         <v>82</v>
       </c>
@@ -3205,7 +3205,7 @@
       <c r="U43" s="18"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="56"/>
+      <c r="A44" s="52"/>
       <c r="B44" s="33" t="s">
         <v>83</v>
       </c>
@@ -3232,7 +3232,7 @@
       <c r="U44" s="28"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="56"/>
+      <c r="A45" s="52"/>
       <c r="B45" s="32" t="s">
         <v>84</v>
       </c>
@@ -3259,7 +3259,7 @@
       <c r="U45" s="18"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="46">
+      <c r="A46" s="51">
         <v>7</v>
       </c>
       <c r="B46" s="34" t="s">
@@ -3308,7 +3308,7 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="46"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="34" t="s">
         <v>86</v>
       </c>
@@ -3355,7 +3355,7 @@
       <c r="U47" s="6"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="46"/>
+      <c r="A48" s="51"/>
       <c r="B48" s="34" t="s">
         <v>87</v>
       </c>
@@ -3402,7 +3402,7 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="46"/>
+      <c r="A49" s="51"/>
       <c r="B49" s="34" t="s">
         <v>88</v>
       </c>
@@ -3449,7 +3449,7 @@
       <c r="U49" s="6"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="46"/>
+      <c r="A50" s="51"/>
       <c r="B50" s="34" t="s">
         <v>89</v>
       </c>
@@ -3461,33 +3461,8 @@
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="5"/>
-      <c r="G50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>46</v>
-      </c>
+      <c r="I50" s="6"/>
+      <c r="L50" s="6"/>
       <c r="P50" s="2"/>
       <c r="Q50" s="4"/>
       <c r="R50" s="6"/>
@@ -3496,7 +3471,7 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="46"/>
+      <c r="A51" s="51"/>
       <c r="B51" s="34" t="s">
         <v>90</v>
       </c>
@@ -3523,7 +3498,7 @@
       <c r="U51" s="6"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="46"/>
+      <c r="A52" s="51"/>
       <c r="B52" s="34" t="s">
         <v>91</v>
       </c>
@@ -3550,7 +3525,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="56">
+      <c r="A53" s="52">
         <v>8</v>
       </c>
       <c r="B53" s="32" t="s">
@@ -3599,7 +3574,7 @@
       <c r="U53" s="18"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="56"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="32" t="s">
         <v>93</v>
       </c>
@@ -3646,7 +3621,7 @@
       <c r="U54" s="18"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="56"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="32" t="s">
         <v>94</v>
       </c>
@@ -3693,7 +3668,7 @@
       <c r="U55" s="18"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="56"/>
+      <c r="A56" s="52"/>
       <c r="B56" s="32" t="s">
         <v>95</v>
       </c>
@@ -3740,7 +3715,7 @@
       <c r="U56" s="18"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="56"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="32" t="s">
         <v>96</v>
       </c>
@@ -3769,7 +3744,7 @@
       <c r="U57" s="18"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="56"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="32" t="s">
         <v>97</v>
       </c>
@@ -3796,7 +3771,7 @@
       <c r="U58" s="18"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="56"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="32" t="s">
         <v>98</v>
       </c>
@@ -3823,7 +3798,7 @@
       <c r="U59" s="18"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="46">
+      <c r="A60" s="51">
         <v>9</v>
       </c>
       <c r="B60" s="34" t="s">
@@ -3872,7 +3847,7 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="46"/>
+      <c r="A61" s="51"/>
       <c r="B61" s="34" t="s">
         <v>100</v>
       </c>
@@ -3919,7 +3894,7 @@
       <c r="U61" s="6"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="46"/>
+      <c r="A62" s="51"/>
       <c r="B62" s="34" t="s">
         <v>101</v>
       </c>
@@ -3966,7 +3941,7 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="46"/>
+      <c r="A63" s="51"/>
       <c r="B63" s="34" t="s">
         <v>102</v>
       </c>
@@ -4013,7 +3988,7 @@
       <c r="U63" s="5"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="46"/>
+      <c r="A64" s="51"/>
       <c r="B64" s="34" t="s">
         <v>103</v>
       </c>
@@ -4042,7 +4017,7 @@
       <c r="U64" s="5"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="46"/>
+      <c r="A65" s="51"/>
       <c r="B65" s="34" t="s">
         <v>104</v>
       </c>
@@ -4069,7 +4044,7 @@
       <c r="U65" s="5"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="46"/>
+      <c r="A66" s="51"/>
       <c r="B66" s="34" t="s">
         <v>105</v>
       </c>
@@ -4096,7 +4071,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="56">
+      <c r="A67" s="52">
         <v>10</v>
       </c>
       <c r="B67" s="32" t="s">
@@ -4145,7 +4120,7 @@
       <c r="U67" s="17"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="56"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="32" t="s">
         <v>107</v>
       </c>
@@ -4192,7 +4167,7 @@
       <c r="U68" s="17"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="56"/>
+      <c r="A69" s="52"/>
       <c r="B69" s="32" t="s">
         <v>108</v>
       </c>
@@ -4239,7 +4214,7 @@
       <c r="U69" s="17"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="56"/>
+      <c r="A70" s="52"/>
       <c r="B70" s="32" t="s">
         <v>109</v>
       </c>
@@ -4286,7 +4261,7 @@
       <c r="U70" s="17"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="56"/>
+      <c r="A71" s="52"/>
       <c r="B71" s="32" t="s">
         <v>110</v>
       </c>
@@ -4315,7 +4290,7 @@
       <c r="U71" s="17"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="56"/>
+      <c r="A72" s="52"/>
       <c r="B72" s="32" t="s">
         <v>111</v>
       </c>
@@ -4325,15 +4300,33 @@
       <c r="D72" s="14"/>
       <c r="E72" s="16"/>
       <c r="F72" s="17"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="16"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="16"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="14"/>
-      <c r="N72" s="16"/>
-      <c r="O72" s="18"/>
+      <c r="G72" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J72" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="N72" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="O72" s="16" t="s">
+        <v>46</v>
+      </c>
       <c r="P72" s="14"/>
       <c r="Q72" s="16"/>
       <c r="R72" s="17"/>
@@ -4342,7 +4335,7 @@
       <c r="U72" s="17"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="56"/>
+      <c r="A73" s="52"/>
       <c r="B73" s="32" t="s">
         <v>112</v>
       </c>
@@ -4369,7 +4362,7 @@
       <c r="U73" s="17"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="46">
+      <c r="A74" s="51">
         <v>11</v>
       </c>
       <c r="B74" s="34" t="s">
@@ -4418,7 +4411,7 @@
       <c r="U74" s="5"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="46"/>
+      <c r="A75" s="51"/>
       <c r="B75" s="34" t="s">
         <v>114</v>
       </c>
@@ -4465,7 +4458,7 @@
       <c r="U75" s="5"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="46"/>
+      <c r="A76" s="51"/>
       <c r="B76" s="34" t="s">
         <v>115</v>
       </c>
@@ -4512,7 +4505,7 @@
       <c r="U76" s="5"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="46"/>
+      <c r="A77" s="51"/>
       <c r="B77" s="34" t="s">
         <v>116</v>
       </c>
@@ -4559,7 +4552,7 @@
       <c r="U77" s="6"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="46"/>
+      <c r="A78" s="51"/>
       <c r="B78" s="34" t="s">
         <v>117</v>
       </c>
@@ -4588,7 +4581,7 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="46"/>
+      <c r="A79" s="51"/>
       <c r="B79" s="34" t="s">
         <v>118</v>
       </c>
@@ -4615,7 +4608,7 @@
       <c r="U79" s="6"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="46"/>
+      <c r="A80" s="51"/>
       <c r="B80" s="34" t="s">
         <v>119</v>
       </c>
@@ -4642,7 +4635,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="56">
+      <c r="A81" s="52">
         <v>12</v>
       </c>
       <c r="B81" s="32" t="s">
@@ -4651,191 +4644,191 @@
       <c r="C81" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="68" t="s">
+      <c r="D81" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="E81" s="69"/>
-      <c r="F81" s="69"/>
-      <c r="G81" s="69"/>
-      <c r="H81" s="69"/>
-      <c r="I81" s="69"/>
-      <c r="J81" s="69"/>
-      <c r="K81" s="69"/>
-      <c r="L81" s="69"/>
-      <c r="M81" s="69"/>
-      <c r="N81" s="69"/>
-      <c r="O81" s="69"/>
-      <c r="P81" s="69"/>
-      <c r="Q81" s="69"/>
-      <c r="R81" s="69"/>
-      <c r="S81" s="69"/>
-      <c r="T81" s="69"/>
-      <c r="U81" s="70"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
+      <c r="H81" s="67"/>
+      <c r="I81" s="67"/>
+      <c r="J81" s="67"/>
+      <c r="K81" s="67"/>
+      <c r="L81" s="67"/>
+      <c r="M81" s="67"/>
+      <c r="N81" s="67"/>
+      <c r="O81" s="67"/>
+      <c r="P81" s="67"/>
+      <c r="Q81" s="67"/>
+      <c r="R81" s="67"/>
+      <c r="S81" s="67"/>
+      <c r="T81" s="67"/>
+      <c r="U81" s="68"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="56"/>
+      <c r="A82" s="52"/>
       <c r="B82" s="32" t="s">
         <v>122</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="71"/>
-      <c r="E82" s="72"/>
-      <c r="F82" s="72"/>
-      <c r="G82" s="72"/>
-      <c r="H82" s="72"/>
-      <c r="I82" s="72"/>
-      <c r="J82" s="72"/>
-      <c r="K82" s="72"/>
-      <c r="L82" s="72"/>
-      <c r="M82" s="72"/>
-      <c r="N82" s="72"/>
-      <c r="O82" s="72"/>
-      <c r="P82" s="72"/>
-      <c r="Q82" s="72"/>
-      <c r="R82" s="72"/>
-      <c r="S82" s="72"/>
-      <c r="T82" s="72"/>
-      <c r="U82" s="73"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="70"/>
+      <c r="I82" s="70"/>
+      <c r="J82" s="70"/>
+      <c r="K82" s="70"/>
+      <c r="L82" s="70"/>
+      <c r="M82" s="70"/>
+      <c r="N82" s="70"/>
+      <c r="O82" s="70"/>
+      <c r="P82" s="70"/>
+      <c r="Q82" s="70"/>
+      <c r="R82" s="70"/>
+      <c r="S82" s="70"/>
+      <c r="T82" s="70"/>
+      <c r="U82" s="71"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="56"/>
+      <c r="A83" s="52"/>
       <c r="B83" s="32" t="s">
         <v>123</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D83" s="71"/>
-      <c r="E83" s="72"/>
-      <c r="F83" s="72"/>
-      <c r="G83" s="72"/>
-      <c r="H83" s="72"/>
-      <c r="I83" s="72"/>
-      <c r="J83" s="72"/>
-      <c r="K83" s="72"/>
-      <c r="L83" s="72"/>
-      <c r="M83" s="72"/>
-      <c r="N83" s="72"/>
-      <c r="O83" s="72"/>
-      <c r="P83" s="72"/>
-      <c r="Q83" s="72"/>
-      <c r="R83" s="72"/>
-      <c r="S83" s="72"/>
-      <c r="T83" s="72"/>
-      <c r="U83" s="73"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="70"/>
+      <c r="G83" s="70"/>
+      <c r="H83" s="70"/>
+      <c r="I83" s="70"/>
+      <c r="J83" s="70"/>
+      <c r="K83" s="70"/>
+      <c r="L83" s="70"/>
+      <c r="M83" s="70"/>
+      <c r="N83" s="70"/>
+      <c r="O83" s="70"/>
+      <c r="P83" s="70"/>
+      <c r="Q83" s="70"/>
+      <c r="R83" s="70"/>
+      <c r="S83" s="70"/>
+      <c r="T83" s="70"/>
+      <c r="U83" s="71"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="56"/>
+      <c r="A84" s="52"/>
       <c r="B84" s="32" t="s">
         <v>124</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D84" s="71"/>
-      <c r="E84" s="72"/>
-      <c r="F84" s="72"/>
-      <c r="G84" s="72"/>
-      <c r="H84" s="72"/>
-      <c r="I84" s="72"/>
-      <c r="J84" s="72"/>
-      <c r="K84" s="72"/>
-      <c r="L84" s="72"/>
-      <c r="M84" s="72"/>
-      <c r="N84" s="72"/>
-      <c r="O84" s="72"/>
-      <c r="P84" s="72"/>
-      <c r="Q84" s="72"/>
-      <c r="R84" s="72"/>
-      <c r="S84" s="72"/>
-      <c r="T84" s="72"/>
-      <c r="U84" s="73"/>
+      <c r="D84" s="69"/>
+      <c r="E84" s="70"/>
+      <c r="F84" s="70"/>
+      <c r="G84" s="70"/>
+      <c r="H84" s="70"/>
+      <c r="I84" s="70"/>
+      <c r="J84" s="70"/>
+      <c r="K84" s="70"/>
+      <c r="L84" s="70"/>
+      <c r="M84" s="70"/>
+      <c r="N84" s="70"/>
+      <c r="O84" s="70"/>
+      <c r="P84" s="70"/>
+      <c r="Q84" s="70"/>
+      <c r="R84" s="70"/>
+      <c r="S84" s="70"/>
+      <c r="T84" s="70"/>
+      <c r="U84" s="71"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="56"/>
+      <c r="A85" s="52"/>
       <c r="B85" s="32" t="s">
         <v>125</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D85" s="71"/>
-      <c r="E85" s="72"/>
-      <c r="F85" s="72"/>
-      <c r="G85" s="72"/>
-      <c r="H85" s="72"/>
-      <c r="I85" s="72"/>
-      <c r="J85" s="72"/>
-      <c r="K85" s="72"/>
-      <c r="L85" s="72"/>
-      <c r="M85" s="72"/>
-      <c r="N85" s="72"/>
-      <c r="O85" s="72"/>
-      <c r="P85" s="72"/>
-      <c r="Q85" s="72"/>
-      <c r="R85" s="72"/>
-      <c r="S85" s="72"/>
-      <c r="T85" s="72"/>
-      <c r="U85" s="73"/>
+      <c r="D85" s="69"/>
+      <c r="E85" s="70"/>
+      <c r="F85" s="70"/>
+      <c r="G85" s="70"/>
+      <c r="H85" s="70"/>
+      <c r="I85" s="70"/>
+      <c r="J85" s="70"/>
+      <c r="K85" s="70"/>
+      <c r="L85" s="70"/>
+      <c r="M85" s="70"/>
+      <c r="N85" s="70"/>
+      <c r="O85" s="70"/>
+      <c r="P85" s="70"/>
+      <c r="Q85" s="70"/>
+      <c r="R85" s="70"/>
+      <c r="S85" s="70"/>
+      <c r="T85" s="70"/>
+      <c r="U85" s="71"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="56"/>
+      <c r="A86" s="52"/>
       <c r="B86" s="32" t="s">
         <v>126</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D86" s="71"/>
-      <c r="E86" s="72"/>
-      <c r="F86" s="72"/>
-      <c r="G86" s="72"/>
-      <c r="H86" s="72"/>
-      <c r="I86" s="72"/>
-      <c r="J86" s="72"/>
-      <c r="K86" s="72"/>
-      <c r="L86" s="72"/>
-      <c r="M86" s="72"/>
-      <c r="N86" s="72"/>
-      <c r="O86" s="72"/>
-      <c r="P86" s="72"/>
-      <c r="Q86" s="72"/>
-      <c r="R86" s="72"/>
-      <c r="S86" s="72"/>
-      <c r="T86" s="72"/>
-      <c r="U86" s="73"/>
+      <c r="D86" s="69"/>
+      <c r="E86" s="70"/>
+      <c r="F86" s="70"/>
+      <c r="G86" s="70"/>
+      <c r="H86" s="70"/>
+      <c r="I86" s="70"/>
+      <c r="J86" s="70"/>
+      <c r="K86" s="70"/>
+      <c r="L86" s="70"/>
+      <c r="M86" s="70"/>
+      <c r="N86" s="70"/>
+      <c r="O86" s="70"/>
+      <c r="P86" s="70"/>
+      <c r="Q86" s="70"/>
+      <c r="R86" s="70"/>
+      <c r="S86" s="70"/>
+      <c r="T86" s="70"/>
+      <c r="U86" s="71"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="56"/>
+      <c r="A87" s="52"/>
       <c r="B87" s="32" t="s">
         <v>127</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D87" s="71"/>
-      <c r="E87" s="72"/>
-      <c r="F87" s="72"/>
-      <c r="G87" s="72"/>
-      <c r="H87" s="72"/>
-      <c r="I87" s="72"/>
-      <c r="J87" s="72"/>
-      <c r="K87" s="72"/>
-      <c r="L87" s="72"/>
-      <c r="M87" s="72"/>
-      <c r="N87" s="72"/>
-      <c r="O87" s="72"/>
-      <c r="P87" s="72"/>
-      <c r="Q87" s="72"/>
-      <c r="R87" s="72"/>
-      <c r="S87" s="72"/>
-      <c r="T87" s="72"/>
-      <c r="U87" s="73"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="70"/>
+      <c r="H87" s="70"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="70"/>
+      <c r="K87" s="70"/>
+      <c r="L87" s="70"/>
+      <c r="M87" s="70"/>
+      <c r="N87" s="70"/>
+      <c r="O87" s="70"/>
+      <c r="P87" s="70"/>
+      <c r="Q87" s="70"/>
+      <c r="R87" s="70"/>
+      <c r="S87" s="70"/>
+      <c r="T87" s="70"/>
+      <c r="U87" s="71"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="46">
+      <c r="A88" s="51">
         <v>13</v>
       </c>
       <c r="B88" s="34" t="s">
@@ -4844,189 +4837,189 @@
       <c r="C88" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="71"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="72"/>
-      <c r="G88" s="72"/>
-      <c r="H88" s="72"/>
-      <c r="I88" s="72"/>
-      <c r="J88" s="72"/>
-      <c r="K88" s="72"/>
-      <c r="L88" s="72"/>
-      <c r="M88" s="72"/>
-      <c r="N88" s="72"/>
-      <c r="O88" s="72"/>
-      <c r="P88" s="72"/>
-      <c r="Q88" s="72"/>
-      <c r="R88" s="72"/>
-      <c r="S88" s="72"/>
-      <c r="T88" s="72"/>
-      <c r="U88" s="73"/>
+      <c r="D88" s="69"/>
+      <c r="E88" s="70"/>
+      <c r="F88" s="70"/>
+      <c r="G88" s="70"/>
+      <c r="H88" s="70"/>
+      <c r="I88" s="70"/>
+      <c r="J88" s="70"/>
+      <c r="K88" s="70"/>
+      <c r="L88" s="70"/>
+      <c r="M88" s="70"/>
+      <c r="N88" s="70"/>
+      <c r="O88" s="70"/>
+      <c r="P88" s="70"/>
+      <c r="Q88" s="70"/>
+      <c r="R88" s="70"/>
+      <c r="S88" s="70"/>
+      <c r="T88" s="70"/>
+      <c r="U88" s="71"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="46"/>
+      <c r="A89" s="51"/>
       <c r="B89" s="34" t="s">
         <v>129</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D89" s="71"/>
-      <c r="E89" s="72"/>
-      <c r="F89" s="72"/>
-      <c r="G89" s="72"/>
-      <c r="H89" s="72"/>
-      <c r="I89" s="72"/>
-      <c r="J89" s="72"/>
-      <c r="K89" s="72"/>
-      <c r="L89" s="72"/>
-      <c r="M89" s="72"/>
-      <c r="N89" s="72"/>
-      <c r="O89" s="72"/>
-      <c r="P89" s="72"/>
-      <c r="Q89" s="72"/>
-      <c r="R89" s="72"/>
-      <c r="S89" s="72"/>
-      <c r="T89" s="72"/>
-      <c r="U89" s="73"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="70"/>
+      <c r="F89" s="70"/>
+      <c r="G89" s="70"/>
+      <c r="H89" s="70"/>
+      <c r="I89" s="70"/>
+      <c r="J89" s="70"/>
+      <c r="K89" s="70"/>
+      <c r="L89" s="70"/>
+      <c r="M89" s="70"/>
+      <c r="N89" s="70"/>
+      <c r="O89" s="70"/>
+      <c r="P89" s="70"/>
+      <c r="Q89" s="70"/>
+      <c r="R89" s="70"/>
+      <c r="S89" s="70"/>
+      <c r="T89" s="70"/>
+      <c r="U89" s="71"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="46"/>
+      <c r="A90" s="51"/>
       <c r="B90" s="34" t="s">
         <v>130</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D90" s="71"/>
-      <c r="E90" s="72"/>
-      <c r="F90" s="72"/>
-      <c r="G90" s="72"/>
-      <c r="H90" s="72"/>
-      <c r="I90" s="72"/>
-      <c r="J90" s="72"/>
-      <c r="K90" s="72"/>
-      <c r="L90" s="72"/>
-      <c r="M90" s="72"/>
-      <c r="N90" s="72"/>
-      <c r="O90" s="72"/>
-      <c r="P90" s="72"/>
-      <c r="Q90" s="72"/>
-      <c r="R90" s="72"/>
-      <c r="S90" s="72"/>
-      <c r="T90" s="72"/>
-      <c r="U90" s="73"/>
+      <c r="D90" s="69"/>
+      <c r="E90" s="70"/>
+      <c r="F90" s="70"/>
+      <c r="G90" s="70"/>
+      <c r="H90" s="70"/>
+      <c r="I90" s="70"/>
+      <c r="J90" s="70"/>
+      <c r="K90" s="70"/>
+      <c r="L90" s="70"/>
+      <c r="M90" s="70"/>
+      <c r="N90" s="70"/>
+      <c r="O90" s="70"/>
+      <c r="P90" s="70"/>
+      <c r="Q90" s="70"/>
+      <c r="R90" s="70"/>
+      <c r="S90" s="70"/>
+      <c r="T90" s="70"/>
+      <c r="U90" s="71"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="46"/>
+      <c r="A91" s="51"/>
       <c r="B91" s="34" t="s">
         <v>131</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D91" s="71"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
-      <c r="G91" s="72"/>
-      <c r="H91" s="72"/>
-      <c r="I91" s="72"/>
-      <c r="J91" s="72"/>
-      <c r="K91" s="72"/>
-      <c r="L91" s="72"/>
-      <c r="M91" s="72"/>
-      <c r="N91" s="72"/>
-      <c r="O91" s="72"/>
-      <c r="P91" s="72"/>
-      <c r="Q91" s="72"/>
-      <c r="R91" s="72"/>
-      <c r="S91" s="72"/>
-      <c r="T91" s="72"/>
-      <c r="U91" s="73"/>
+      <c r="D91" s="69"/>
+      <c r="E91" s="70"/>
+      <c r="F91" s="70"/>
+      <c r="G91" s="70"/>
+      <c r="H91" s="70"/>
+      <c r="I91" s="70"/>
+      <c r="J91" s="70"/>
+      <c r="K91" s="70"/>
+      <c r="L91" s="70"/>
+      <c r="M91" s="70"/>
+      <c r="N91" s="70"/>
+      <c r="O91" s="70"/>
+      <c r="P91" s="70"/>
+      <c r="Q91" s="70"/>
+      <c r="R91" s="70"/>
+      <c r="S91" s="70"/>
+      <c r="T91" s="70"/>
+      <c r="U91" s="71"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="46"/>
+      <c r="A92" s="51"/>
       <c r="B92" s="34" t="s">
         <v>132</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D92" s="71"/>
-      <c r="E92" s="72"/>
-      <c r="F92" s="72"/>
-      <c r="G92" s="72"/>
-      <c r="H92" s="72"/>
-      <c r="I92" s="72"/>
-      <c r="J92" s="72"/>
-      <c r="K92" s="72"/>
-      <c r="L92" s="72"/>
-      <c r="M92" s="72"/>
-      <c r="N92" s="72"/>
-      <c r="O92" s="72"/>
-      <c r="P92" s="72"/>
-      <c r="Q92" s="72"/>
-      <c r="R92" s="72"/>
-      <c r="S92" s="72"/>
-      <c r="T92" s="72"/>
-      <c r="U92" s="73"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="70"/>
+      <c r="F92" s="70"/>
+      <c r="G92" s="70"/>
+      <c r="H92" s="70"/>
+      <c r="I92" s="70"/>
+      <c r="J92" s="70"/>
+      <c r="K92" s="70"/>
+      <c r="L92" s="70"/>
+      <c r="M92" s="70"/>
+      <c r="N92" s="70"/>
+      <c r="O92" s="70"/>
+      <c r="P92" s="70"/>
+      <c r="Q92" s="70"/>
+      <c r="R92" s="70"/>
+      <c r="S92" s="70"/>
+      <c r="T92" s="70"/>
+      <c r="U92" s="71"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="46"/>
+      <c r="A93" s="51"/>
       <c r="B93" s="34" t="s">
         <v>133</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D93" s="71"/>
-      <c r="E93" s="72"/>
-      <c r="F93" s="72"/>
-      <c r="G93" s="72"/>
-      <c r="H93" s="72"/>
-      <c r="I93" s="72"/>
-      <c r="J93" s="72"/>
-      <c r="K93" s="72"/>
-      <c r="L93" s="72"/>
-      <c r="M93" s="72"/>
-      <c r="N93" s="72"/>
-      <c r="O93" s="72"/>
-      <c r="P93" s="72"/>
-      <c r="Q93" s="72"/>
-      <c r="R93" s="72"/>
-      <c r="S93" s="72"/>
-      <c r="T93" s="72"/>
-      <c r="U93" s="73"/>
+      <c r="D93" s="69"/>
+      <c r="E93" s="70"/>
+      <c r="F93" s="70"/>
+      <c r="G93" s="70"/>
+      <c r="H93" s="70"/>
+      <c r="I93" s="70"/>
+      <c r="J93" s="70"/>
+      <c r="K93" s="70"/>
+      <c r="L93" s="70"/>
+      <c r="M93" s="70"/>
+      <c r="N93" s="70"/>
+      <c r="O93" s="70"/>
+      <c r="P93" s="70"/>
+      <c r="Q93" s="70"/>
+      <c r="R93" s="70"/>
+      <c r="S93" s="70"/>
+      <c r="T93" s="70"/>
+      <c r="U93" s="71"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="46"/>
+      <c r="A94" s="51"/>
       <c r="B94" s="34" t="s">
         <v>134</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D94" s="74"/>
-      <c r="E94" s="75"/>
-      <c r="F94" s="75"/>
-      <c r="G94" s="75"/>
-      <c r="H94" s="75"/>
-      <c r="I94" s="75"/>
-      <c r="J94" s="75"/>
-      <c r="K94" s="75"/>
-      <c r="L94" s="75"/>
-      <c r="M94" s="75"/>
-      <c r="N94" s="75"/>
-      <c r="O94" s="75"/>
-      <c r="P94" s="75"/>
-      <c r="Q94" s="75"/>
-      <c r="R94" s="75"/>
-      <c r="S94" s="75"/>
-      <c r="T94" s="75"/>
-      <c r="U94" s="76"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="73"/>
+      <c r="F94" s="73"/>
+      <c r="G94" s="73"/>
+      <c r="H94" s="73"/>
+      <c r="I94" s="73"/>
+      <c r="J94" s="73"/>
+      <c r="K94" s="73"/>
+      <c r="L94" s="73"/>
+      <c r="M94" s="73"/>
+      <c r="N94" s="73"/>
+      <c r="O94" s="73"/>
+      <c r="P94" s="73"/>
+      <c r="Q94" s="73"/>
+      <c r="R94" s="73"/>
+      <c r="S94" s="73"/>
+      <c r="T94" s="73"/>
+      <c r="U94" s="74"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="56">
+      <c r="A95" s="52">
         <v>14</v>
       </c>
       <c r="B95" s="32" t="s">
@@ -5059,7 +5052,7 @@
       <c r="U95" s="18"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="56"/>
+      <c r="A96" s="52"/>
       <c r="B96" s="32" t="s">
         <v>137</v>
       </c>
@@ -5090,7 +5083,7 @@
       <c r="U96" s="18"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="56"/>
+      <c r="A97" s="52"/>
       <c r="B97" s="32" t="s">
         <v>138</v>
       </c>
@@ -5121,7 +5114,7 @@
       <c r="U97" s="18"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="56"/>
+      <c r="A98" s="52"/>
       <c r="B98" s="32" t="s">
         <v>139</v>
       </c>
@@ -5152,7 +5145,7 @@
       <c r="U98" s="18"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="56"/>
+      <c r="A99" s="52"/>
       <c r="B99" s="32" t="s">
         <v>140</v>
       </c>
@@ -5183,7 +5176,7 @@
       <c r="U99" s="18"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="56"/>
+      <c r="A100" s="52"/>
       <c r="B100" s="32" t="s">
         <v>141</v>
       </c>
@@ -5214,7 +5207,7 @@
       <c r="U100" s="18"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="56"/>
+      <c r="A101" s="52"/>
       <c r="B101" s="32" t="s">
         <v>142</v>
       </c>
@@ -5245,7 +5238,7 @@
       <c r="U101" s="18"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="46">
+      <c r="A102" s="51">
         <v>15</v>
       </c>
       <c r="B102" s="34" t="s">
@@ -5278,7 +5271,7 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="46"/>
+      <c r="A103" s="51"/>
       <c r="B103" s="34" t="s">
         <v>144</v>
       </c>
@@ -5309,7 +5302,7 @@
       <c r="U103" s="6"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="46"/>
+      <c r="A104" s="51"/>
       <c r="B104" s="34" t="s">
         <v>145</v>
       </c>
@@ -5340,7 +5333,7 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="46"/>
+      <c r="A105" s="51"/>
       <c r="B105" s="34" t="s">
         <v>146</v>
       </c>
@@ -5371,7 +5364,7 @@
       <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="46"/>
+      <c r="A106" s="51"/>
       <c r="B106" s="34" t="s">
         <v>147</v>
       </c>
@@ -5402,7 +5395,7 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="46"/>
+      <c r="A107" s="51"/>
       <c r="B107" s="34" t="s">
         <v>148</v>
       </c>
@@ -5433,7 +5426,7 @@
       <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="46"/>
+      <c r="A108" s="51"/>
       <c r="B108" s="34" t="s">
         <v>149</v>
       </c>
@@ -5464,7 +5457,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="56">
+      <c r="A109" s="52">
         <v>16</v>
       </c>
       <c r="B109" s="32" t="s">
@@ -5497,7 +5490,7 @@
       <c r="U109" s="17"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="56"/>
+      <c r="A110" s="52"/>
       <c r="B110" s="32" t="s">
         <v>151</v>
       </c>
@@ -5528,7 +5521,7 @@
       <c r="U110" s="17"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="56"/>
+      <c r="A111" s="52"/>
       <c r="B111" s="32" t="s">
         <v>152</v>
       </c>
@@ -5559,7 +5552,7 @@
       <c r="U111" s="17"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="56"/>
+      <c r="A112" s="52"/>
       <c r="B112" s="32" t="s">
         <v>153</v>
       </c>
@@ -5590,7 +5583,7 @@
       <c r="U112" s="17"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="56"/>
+      <c r="A113" s="52"/>
       <c r="B113" s="32" t="s">
         <v>154</v>
       </c>
@@ -5621,7 +5614,7 @@
       <c r="U113" s="17"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="56"/>
+      <c r="A114" s="52"/>
       <c r="B114" s="32" t="s">
         <v>155</v>
       </c>
@@ -5652,7 +5645,7 @@
       <c r="U114" s="17"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="56"/>
+      <c r="A115" s="52"/>
       <c r="B115" s="32" t="s">
         <v>156</v>
       </c>
@@ -5683,7 +5676,7 @@
       <c r="U115" s="17"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="46">
+      <c r="A116" s="51">
         <v>17</v>
       </c>
       <c r="B116" s="34" t="s">
@@ -5716,7 +5709,7 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="46"/>
+      <c r="A117" s="51"/>
       <c r="B117" s="34" t="s">
         <v>158</v>
       </c>
@@ -5747,7 +5740,7 @@
       <c r="U117" s="6"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="46"/>
+      <c r="A118" s="51"/>
       <c r="B118" s="34" t="s">
         <v>159</v>
       </c>
@@ -5778,7 +5771,7 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="46"/>
+      <c r="A119" s="51"/>
       <c r="B119" s="34" t="s">
         <v>160</v>
       </c>
@@ -5809,7 +5802,7 @@
       <c r="U119" s="6"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="46"/>
+      <c r="A120" s="51"/>
       <c r="B120" s="34" t="s">
         <v>161</v>
       </c>
@@ -5840,7 +5833,7 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="46"/>
+      <c r="A121" s="51"/>
       <c r="B121" s="34" t="s">
         <v>162</v>
       </c>
@@ -5871,7 +5864,7 @@
       <c r="U121" s="6"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="46"/>
+      <c r="A122" s="51"/>
       <c r="B122" s="34" t="s">
         <v>163</v>
       </c>
@@ -5902,7 +5895,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="56">
+      <c r="A123" s="52">
         <v>18</v>
       </c>
       <c r="B123" s="32" t="s">
@@ -5935,7 +5928,7 @@
       <c r="U123" s="17"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="56"/>
+      <c r="A124" s="52"/>
       <c r="B124" s="32" t="s">
         <v>165</v>
       </c>
@@ -5966,7 +5959,7 @@
       <c r="U124" s="17"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="56"/>
+      <c r="A125" s="52"/>
       <c r="B125" s="32" t="s">
         <v>166</v>
       </c>
@@ -5997,7 +5990,7 @@
       <c r="U125" s="17"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="56"/>
+      <c r="A126" s="52"/>
       <c r="B126" s="32" t="s">
         <v>167</v>
       </c>
@@ -6028,36 +6021,36 @@
       <c r="U126" s="17"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="56"/>
+      <c r="A127" s="52"/>
       <c r="B127" s="31" t="s">
         <v>168</v>
       </c>
       <c r="C127" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D127" s="65" t="s">
+      <c r="D127" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E127" s="66"/>
-      <c r="F127" s="66"/>
-      <c r="G127" s="66"/>
-      <c r="H127" s="66"/>
-      <c r="I127" s="66"/>
-      <c r="J127" s="66"/>
-      <c r="K127" s="66"/>
-      <c r="L127" s="66"/>
-      <c r="M127" s="66"/>
-      <c r="N127" s="66"/>
-      <c r="O127" s="66"/>
-      <c r="P127" s="66"/>
-      <c r="Q127" s="66"/>
-      <c r="R127" s="66"/>
-      <c r="S127" s="66"/>
-      <c r="T127" s="66"/>
-      <c r="U127" s="67"/>
+      <c r="E127" s="64"/>
+      <c r="F127" s="64"/>
+      <c r="G127" s="64"/>
+      <c r="H127" s="64"/>
+      <c r="I127" s="64"/>
+      <c r="J127" s="64"/>
+      <c r="K127" s="64"/>
+      <c r="L127" s="64"/>
+      <c r="M127" s="64"/>
+      <c r="N127" s="64"/>
+      <c r="O127" s="64"/>
+      <c r="P127" s="64"/>
+      <c r="Q127" s="64"/>
+      <c r="R127" s="64"/>
+      <c r="S127" s="64"/>
+      <c r="T127" s="64"/>
+      <c r="U127" s="65"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="56"/>
+      <c r="A128" s="52"/>
       <c r="B128" s="32" t="s">
         <v>169</v>
       </c>
@@ -6088,7 +6081,7 @@
       <c r="U128" s="17"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="56"/>
+      <c r="A129" s="52"/>
       <c r="B129" s="32" t="s">
         <v>170</v>
       </c>
@@ -6119,7 +6112,7 @@
       <c r="U129" s="17"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="46">
+      <c r="A130" s="51">
         <v>19</v>
       </c>
       <c r="B130" s="34" t="s">
@@ -6152,7 +6145,7 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="46"/>
+      <c r="A131" s="51"/>
       <c r="B131" s="34" t="s">
         <v>172</v>
       </c>
@@ -6183,7 +6176,7 @@
       <c r="U131" s="6"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="46"/>
+      <c r="A132" s="51"/>
       <c r="B132" s="34" t="s">
         <v>173</v>
       </c>
@@ -6214,7 +6207,7 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="46"/>
+      <c r="A133" s="51"/>
       <c r="B133" s="34" t="s">
         <v>174</v>
       </c>
@@ -6245,7 +6238,7 @@
       <c r="U133" s="6"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="46"/>
+      <c r="A134" s="51"/>
       <c r="B134" s="34" t="s">
         <v>175</v>
       </c>
@@ -6276,7 +6269,7 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="46"/>
+      <c r="A135" s="51"/>
       <c r="B135" s="34" t="s">
         <v>176</v>
       </c>
@@ -6307,7 +6300,7 @@
       <c r="U135" s="6"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="46"/>
+      <c r="A136" s="51"/>
       <c r="B136" s="34" t="s">
         <v>177</v>
       </c>
@@ -6353,6 +6346,32 @@
     <row r="150" ht="20.45"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="D29:U31"/>
+    <mergeCell ref="D35:U41"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="S2:U2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="A39:A45"/>
     <mergeCell ref="A74:A80"/>
     <mergeCell ref="A123:A129"/>
     <mergeCell ref="D127:U127"/>
@@ -6364,32 +6383,6 @@
     <mergeCell ref="A109:A115"/>
     <mergeCell ref="A116:A122"/>
     <mergeCell ref="A81:A87"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="A32:A38"/>
-    <mergeCell ref="D35:U41"/>
-    <mergeCell ref="A39:A45"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="S2:U2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6432,81 +6425,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="57" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="57" t="s">
+      <c r="E2" s="76"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="58"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="57" t="s">
+      <c r="H2" s="76"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="58"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="57" t="s">
+      <c r="K2" s="76"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="58"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="57" t="s">
+      <c r="N2" s="76"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="57" t="s">
+      <c r="Q2" s="76"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="58"/>
-      <c r="U2" s="59"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="77"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="57" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="58"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="57" t="s">
+      <c r="E3" s="76"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="58"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="57" t="s">
+      <c r="H3" s="76"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="58"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="57" t="s">
+      <c r="K3" s="76"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="58"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="57" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="57" t="s">
+      <c r="Q3" s="76"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="58"/>
-      <c r="U3" s="59"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="46">
+      <c r="A4" s="51">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -6564,7 +6557,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="46"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
@@ -6610,7 +6603,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="46"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
@@ -6654,7 +6647,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="46"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
@@ -6718,7 +6711,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="46"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
@@ -6762,7 +6755,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="46"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
@@ -6806,7 +6799,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="46"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
@@ -6848,7 +6841,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="56">
+      <c r="A11" s="52">
         <v>2</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -6914,7 +6907,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="56"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="14" t="s">
         <v>47</v>
       </c>
@@ -6976,7 +6969,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="56"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="14" t="s">
         <v>50</v>
       </c>
@@ -7038,7 +7031,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="56"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="14" t="s">
         <v>51</v>
       </c>
@@ -7090,7 +7083,7 @@
       <c r="AA14" s="10"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="56"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="14" t="s">
         <v>52</v>
       </c>
@@ -7142,7 +7135,7 @@
       <c r="AA15" s="10"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="56"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="14" t="s">
         <v>53</v>
       </c>
@@ -7181,7 +7174,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="56"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="14" t="s">
         <v>55</v>
       </c>
@@ -7208,7 +7201,7 @@
       <c r="U17" s="18"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="46">
+      <c r="A18" s="51">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -7257,7 +7250,7 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="46"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -7304,7 +7297,7 @@
       <c r="U19" s="6"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="46"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -7351,7 +7344,7 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="46"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
@@ -7398,7 +7391,7 @@
       <c r="U21" s="6"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="46"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="2" t="s">
         <v>60</v>
       </c>
@@ -7427,7 +7420,7 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="46"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
@@ -7454,7 +7447,7 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="46"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="24" t="s">
         <v>62</v>
       </c>
@@ -7481,7 +7474,7 @@
       <c r="U24" s="28"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="56">
+      <c r="A25" s="52">
         <v>4</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -7530,7 +7523,7 @@
       <c r="U25" s="18"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="56"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="14" t="s">
         <v>64</v>
       </c>
@@ -7577,7 +7570,7 @@
       <c r="U26" s="18"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="56"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="14" t="s">
         <v>65</v>
       </c>
@@ -7624,7 +7617,7 @@
       <c r="U27" s="18"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="56"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="14" t="s">
         <v>66</v>
       </c>
@@ -7671,90 +7664,90 @@
       <c r="U28" s="18"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="56"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="29" t="s">
         <v>67</v>
       </c>
       <c r="C29" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="49"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="55"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="56"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="29" t="s">
         <v>69</v>
       </c>
       <c r="C30" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="50"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="51"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="52"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="58"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="56"/>
+      <c r="A31" s="52"/>
       <c r="B31" s="29" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="53"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="54"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="54"/>
-      <c r="R31" s="54"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="54"/>
-      <c r="U31" s="55"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="46">
+      <c r="A32" s="51">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -7803,7 +7796,7 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="46"/>
+      <c r="A33" s="51"/>
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
@@ -7850,7 +7843,7 @@
       <c r="U33" s="6"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="46"/>
+      <c r="A34" s="51"/>
       <c r="B34" s="2" t="s">
         <v>73</v>
       </c>
@@ -7897,117 +7890,117 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="46"/>
+      <c r="A35" s="51"/>
       <c r="B35" s="31" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="48"/>
-      <c r="R35" s="48"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="48"/>
-      <c r="U35" s="49"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="46"/>
+      <c r="A36" s="51"/>
       <c r="B36" s="31" t="s">
         <v>75</v>
       </c>
       <c r="C36" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="50"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="51"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="51"/>
-      <c r="S36" s="51"/>
-      <c r="T36" s="51"/>
-      <c r="U36" s="52"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="57"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="58"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="46"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="31" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="50"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="51"/>
-      <c r="M37" s="51"/>
-      <c r="N37" s="51"/>
-      <c r="O37" s="51"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="51"/>
-      <c r="S37" s="51"/>
-      <c r="T37" s="51"/>
-      <c r="U37" s="52"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="58"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="46"/>
+      <c r="A38" s="51"/>
       <c r="B38" s="31" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="51"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="51"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="51"/>
-      <c r="R38" s="51"/>
-      <c r="S38" s="51"/>
-      <c r="T38" s="51"/>
-      <c r="U38" s="52"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="58"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="56">
+      <c r="A39" s="52">
         <v>6</v>
       </c>
       <c r="B39" s="31" t="s">
@@ -8016,81 +8009,81 @@
       <c r="C39" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="50"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="51"/>
-      <c r="L39" s="51"/>
-      <c r="M39" s="51"/>
-      <c r="N39" s="51"/>
-      <c r="O39" s="51"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="51"/>
-      <c r="R39" s="51"/>
-      <c r="S39" s="51"/>
-      <c r="T39" s="51"/>
-      <c r="U39" s="52"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="58"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="56"/>
+      <c r="A40" s="52"/>
       <c r="B40" s="31" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="50"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="51"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="51"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="51"/>
-      <c r="R40" s="51"/>
-      <c r="S40" s="51"/>
-      <c r="T40" s="51"/>
-      <c r="U40" s="52"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
+      <c r="P40" s="57"/>
+      <c r="Q40" s="57"/>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="58"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="56"/>
+      <c r="A41" s="52"/>
       <c r="B41" s="31" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="53"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="54"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="54"/>
-      <c r="N41" s="54"/>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="54"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="55"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="61"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="56"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="32" t="s">
         <v>81</v>
       </c>
@@ -8137,7 +8130,7 @@
       <c r="U42" s="18"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="56"/>
+      <c r="A43" s="52"/>
       <c r="B43" s="32" t="s">
         <v>82</v>
       </c>
@@ -8166,7 +8159,7 @@
       <c r="U43" s="18"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="56"/>
+      <c r="A44" s="52"/>
       <c r="B44" s="33" t="s">
         <v>83</v>
       </c>
@@ -8193,7 +8186,7 @@
       <c r="U44" s="28"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="56"/>
+      <c r="A45" s="52"/>
       <c r="B45" s="32" t="s">
         <v>84</v>
       </c>
@@ -8220,7 +8213,7 @@
       <c r="U45" s="18"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="46">
+      <c r="A46" s="51">
         <v>7</v>
       </c>
       <c r="B46" s="34" t="s">
@@ -8269,7 +8262,7 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="46"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="34" t="s">
         <v>86</v>
       </c>
@@ -8316,7 +8309,7 @@
       <c r="U47" s="6"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="46"/>
+      <c r="A48" s="51"/>
       <c r="B48" s="34" t="s">
         <v>87</v>
       </c>
@@ -8363,7 +8356,7 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="46"/>
+      <c r="A49" s="51"/>
       <c r="B49" s="34" t="s">
         <v>88</v>
       </c>
@@ -8410,7 +8403,7 @@
       <c r="U49" s="6"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="46"/>
+      <c r="A50" s="51"/>
       <c r="B50" s="34" t="s">
         <v>89</v>
       </c>
@@ -8439,7 +8432,7 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="46"/>
+      <c r="A51" s="51"/>
       <c r="B51" s="34" t="s">
         <v>90</v>
       </c>
@@ -8466,7 +8459,7 @@
       <c r="U51" s="6"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="46"/>
+      <c r="A52" s="51"/>
       <c r="B52" s="34" t="s">
         <v>91</v>
       </c>
@@ -8493,7 +8486,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="56">
+      <c r="A53" s="52">
         <v>8</v>
       </c>
       <c r="B53" s="32" t="s">
@@ -8542,7 +8535,7 @@
       <c r="U53" s="18"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="56"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="32" t="s">
         <v>93</v>
       </c>
@@ -8589,7 +8582,7 @@
       <c r="U54" s="18"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="56"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="32" t="s">
         <v>94</v>
       </c>
@@ -8636,7 +8629,7 @@
       <c r="U55" s="18"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="56"/>
+      <c r="A56" s="52"/>
       <c r="B56" s="32" t="s">
         <v>95</v>
       </c>
@@ -8683,7 +8676,7 @@
       <c r="U56" s="18"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="56"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="32" t="s">
         <v>96</v>
       </c>
@@ -8730,7 +8723,7 @@
       <c r="U57" s="18"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="56"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="32" t="s">
         <v>97</v>
       </c>
@@ -8757,7 +8750,7 @@
       <c r="U58" s="18"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="56"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="32" t="s">
         <v>98</v>
       </c>
@@ -8784,7 +8777,7 @@
       <c r="U59" s="18"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="46">
+      <c r="A60" s="51">
         <v>9</v>
       </c>
       <c r="B60" s="34" t="s">
@@ -8833,7 +8826,7 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="46"/>
+      <c r="A61" s="51"/>
       <c r="B61" s="34" t="s">
         <v>100</v>
       </c>
@@ -8880,7 +8873,7 @@
       <c r="U61" s="6"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="46"/>
+      <c r="A62" s="51"/>
       <c r="B62" s="34" t="s">
         <v>101</v>
       </c>
@@ -8927,7 +8920,7 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="46"/>
+      <c r="A63" s="51"/>
       <c r="B63" s="34" t="s">
         <v>102</v>
       </c>
@@ -8974,7 +8967,7 @@
       <c r="U63" s="5"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="46"/>
+      <c r="A64" s="51"/>
       <c r="B64" s="34" t="s">
         <v>103</v>
       </c>
@@ -9003,7 +8996,7 @@
       <c r="U64" s="5"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="46"/>
+      <c r="A65" s="51"/>
       <c r="B65" s="34" t="s">
         <v>104</v>
       </c>
@@ -9030,7 +9023,7 @@
       <c r="U65" s="5"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="46"/>
+      <c r="A66" s="51"/>
       <c r="B66" s="34" t="s">
         <v>105</v>
       </c>
@@ -9057,7 +9050,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="56">
+      <c r="A67" s="52">
         <v>10</v>
       </c>
       <c r="B67" s="32" t="s">
@@ -9106,7 +9099,7 @@
       <c r="U67" s="17"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="56"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="32" t="s">
         <v>107</v>
       </c>
@@ -9153,7 +9146,7 @@
       <c r="U68" s="17"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="56"/>
+      <c r="A69" s="52"/>
       <c r="B69" s="32" t="s">
         <v>108</v>
       </c>
@@ -9200,7 +9193,7 @@
       <c r="U69" s="17"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="56"/>
+      <c r="A70" s="52"/>
       <c r="B70" s="32" t="s">
         <v>109</v>
       </c>
@@ -9247,7 +9240,7 @@
       <c r="U70" s="17"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="56"/>
+      <c r="A71" s="52"/>
       <c r="B71" s="32" t="s">
         <v>110</v>
       </c>
@@ -9276,7 +9269,7 @@
       <c r="U71" s="17"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="56"/>
+      <c r="A72" s="52"/>
       <c r="B72" s="32" t="s">
         <v>111</v>
       </c>
@@ -9303,7 +9296,7 @@
       <c r="U72" s="17"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="56"/>
+      <c r="A73" s="52"/>
       <c r="B73" s="32" t="s">
         <v>112</v>
       </c>
@@ -9330,7 +9323,7 @@
       <c r="U73" s="17"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="46">
+      <c r="A74" s="51">
         <v>11</v>
       </c>
       <c r="B74" s="34" t="s">
@@ -9379,7 +9372,7 @@
       <c r="U74" s="5"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="46"/>
+      <c r="A75" s="51"/>
       <c r="B75" s="34" t="s">
         <v>114</v>
       </c>
@@ -9426,7 +9419,7 @@
       <c r="U75" s="5"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="46"/>
+      <c r="A76" s="51"/>
       <c r="B76" s="34" t="s">
         <v>115</v>
       </c>
@@ -9473,7 +9466,7 @@
       <c r="U76" s="5"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="46"/>
+      <c r="A77" s="51"/>
       <c r="B77" s="34" t="s">
         <v>116</v>
       </c>
@@ -9520,7 +9513,7 @@
       <c r="U77" s="6"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="46"/>
+      <c r="A78" s="51"/>
       <c r="B78" s="34" t="s">
         <v>117</v>
       </c>
@@ -9549,7 +9542,7 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="46"/>
+      <c r="A79" s="51"/>
       <c r="B79" s="34" t="s">
         <v>118</v>
       </c>
@@ -9576,7 +9569,7 @@
       <c r="U79" s="6"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="46"/>
+      <c r="A80" s="51"/>
       <c r="B80" s="34" t="s">
         <v>119</v>
       </c>
@@ -9603,7 +9596,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="56">
+      <c r="A81" s="52">
         <v>12</v>
       </c>
       <c r="B81" s="32" t="s">
@@ -9612,191 +9605,191 @@
       <c r="C81" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="68" t="s">
+      <c r="D81" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="E81" s="69"/>
-      <c r="F81" s="69"/>
-      <c r="G81" s="69"/>
-      <c r="H81" s="69"/>
-      <c r="I81" s="69"/>
-      <c r="J81" s="69"/>
-      <c r="K81" s="69"/>
-      <c r="L81" s="69"/>
-      <c r="M81" s="69"/>
-      <c r="N81" s="69"/>
-      <c r="O81" s="69"/>
-      <c r="P81" s="69"/>
-      <c r="Q81" s="69"/>
-      <c r="R81" s="69"/>
-      <c r="S81" s="69"/>
-      <c r="T81" s="69"/>
-      <c r="U81" s="70"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
+      <c r="H81" s="67"/>
+      <c r="I81" s="67"/>
+      <c r="J81" s="67"/>
+      <c r="K81" s="67"/>
+      <c r="L81" s="67"/>
+      <c r="M81" s="67"/>
+      <c r="N81" s="67"/>
+      <c r="O81" s="67"/>
+      <c r="P81" s="67"/>
+      <c r="Q81" s="67"/>
+      <c r="R81" s="67"/>
+      <c r="S81" s="67"/>
+      <c r="T81" s="67"/>
+      <c r="U81" s="68"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="56"/>
+      <c r="A82" s="52"/>
       <c r="B82" s="32" t="s">
         <v>122</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="71"/>
-      <c r="E82" s="72"/>
-      <c r="F82" s="72"/>
-      <c r="G82" s="72"/>
-      <c r="H82" s="72"/>
-      <c r="I82" s="72"/>
-      <c r="J82" s="72"/>
-      <c r="K82" s="72"/>
-      <c r="L82" s="72"/>
-      <c r="M82" s="72"/>
-      <c r="N82" s="72"/>
-      <c r="O82" s="72"/>
-      <c r="P82" s="72"/>
-      <c r="Q82" s="72"/>
-      <c r="R82" s="72"/>
-      <c r="S82" s="72"/>
-      <c r="T82" s="72"/>
-      <c r="U82" s="73"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="70"/>
+      <c r="I82" s="70"/>
+      <c r="J82" s="70"/>
+      <c r="K82" s="70"/>
+      <c r="L82" s="70"/>
+      <c r="M82" s="70"/>
+      <c r="N82" s="70"/>
+      <c r="O82" s="70"/>
+      <c r="P82" s="70"/>
+      <c r="Q82" s="70"/>
+      <c r="R82" s="70"/>
+      <c r="S82" s="70"/>
+      <c r="T82" s="70"/>
+      <c r="U82" s="71"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="56"/>
+      <c r="A83" s="52"/>
       <c r="B83" s="32" t="s">
         <v>123</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D83" s="71"/>
-      <c r="E83" s="72"/>
-      <c r="F83" s="72"/>
-      <c r="G83" s="72"/>
-      <c r="H83" s="72"/>
-      <c r="I83" s="72"/>
-      <c r="J83" s="72"/>
-      <c r="K83" s="72"/>
-      <c r="L83" s="72"/>
-      <c r="M83" s="72"/>
-      <c r="N83" s="72"/>
-      <c r="O83" s="72"/>
-      <c r="P83" s="72"/>
-      <c r="Q83" s="72"/>
-      <c r="R83" s="72"/>
-      <c r="S83" s="72"/>
-      <c r="T83" s="72"/>
-      <c r="U83" s="73"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="70"/>
+      <c r="G83" s="70"/>
+      <c r="H83" s="70"/>
+      <c r="I83" s="70"/>
+      <c r="J83" s="70"/>
+      <c r="K83" s="70"/>
+      <c r="L83" s="70"/>
+      <c r="M83" s="70"/>
+      <c r="N83" s="70"/>
+      <c r="O83" s="70"/>
+      <c r="P83" s="70"/>
+      <c r="Q83" s="70"/>
+      <c r="R83" s="70"/>
+      <c r="S83" s="70"/>
+      <c r="T83" s="70"/>
+      <c r="U83" s="71"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="56"/>
+      <c r="A84" s="52"/>
       <c r="B84" s="32" t="s">
         <v>124</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D84" s="71"/>
-      <c r="E84" s="72"/>
-      <c r="F84" s="72"/>
-      <c r="G84" s="72"/>
-      <c r="H84" s="72"/>
-      <c r="I84" s="72"/>
-      <c r="J84" s="72"/>
-      <c r="K84" s="72"/>
-      <c r="L84" s="72"/>
-      <c r="M84" s="72"/>
-      <c r="N84" s="72"/>
-      <c r="O84" s="72"/>
-      <c r="P84" s="72"/>
-      <c r="Q84" s="72"/>
-      <c r="R84" s="72"/>
-      <c r="S84" s="72"/>
-      <c r="T84" s="72"/>
-      <c r="U84" s="73"/>
+      <c r="D84" s="69"/>
+      <c r="E84" s="70"/>
+      <c r="F84" s="70"/>
+      <c r="G84" s="70"/>
+      <c r="H84" s="70"/>
+      <c r="I84" s="70"/>
+      <c r="J84" s="70"/>
+      <c r="K84" s="70"/>
+      <c r="L84" s="70"/>
+      <c r="M84" s="70"/>
+      <c r="N84" s="70"/>
+      <c r="O84" s="70"/>
+      <c r="P84" s="70"/>
+      <c r="Q84" s="70"/>
+      <c r="R84" s="70"/>
+      <c r="S84" s="70"/>
+      <c r="T84" s="70"/>
+      <c r="U84" s="71"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="56"/>
+      <c r="A85" s="52"/>
       <c r="B85" s="32" t="s">
         <v>125</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D85" s="71"/>
-      <c r="E85" s="72"/>
-      <c r="F85" s="72"/>
-      <c r="G85" s="72"/>
-      <c r="H85" s="72"/>
-      <c r="I85" s="72"/>
-      <c r="J85" s="72"/>
-      <c r="K85" s="72"/>
-      <c r="L85" s="72"/>
-      <c r="M85" s="72"/>
-      <c r="N85" s="72"/>
-      <c r="O85" s="72"/>
-      <c r="P85" s="72"/>
-      <c r="Q85" s="72"/>
-      <c r="R85" s="72"/>
-      <c r="S85" s="72"/>
-      <c r="T85" s="72"/>
-      <c r="U85" s="73"/>
+      <c r="D85" s="69"/>
+      <c r="E85" s="70"/>
+      <c r="F85" s="70"/>
+      <c r="G85" s="70"/>
+      <c r="H85" s="70"/>
+      <c r="I85" s="70"/>
+      <c r="J85" s="70"/>
+      <c r="K85" s="70"/>
+      <c r="L85" s="70"/>
+      <c r="M85" s="70"/>
+      <c r="N85" s="70"/>
+      <c r="O85" s="70"/>
+      <c r="P85" s="70"/>
+      <c r="Q85" s="70"/>
+      <c r="R85" s="70"/>
+      <c r="S85" s="70"/>
+      <c r="T85" s="70"/>
+      <c r="U85" s="71"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="56"/>
+      <c r="A86" s="52"/>
       <c r="B86" s="32" t="s">
         <v>126</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D86" s="71"/>
-      <c r="E86" s="72"/>
-      <c r="F86" s="72"/>
-      <c r="G86" s="72"/>
-      <c r="H86" s="72"/>
-      <c r="I86" s="72"/>
-      <c r="J86" s="72"/>
-      <c r="K86" s="72"/>
-      <c r="L86" s="72"/>
-      <c r="M86" s="72"/>
-      <c r="N86" s="72"/>
-      <c r="O86" s="72"/>
-      <c r="P86" s="72"/>
-      <c r="Q86" s="72"/>
-      <c r="R86" s="72"/>
-      <c r="S86" s="72"/>
-      <c r="T86" s="72"/>
-      <c r="U86" s="73"/>
+      <c r="D86" s="69"/>
+      <c r="E86" s="70"/>
+      <c r="F86" s="70"/>
+      <c r="G86" s="70"/>
+      <c r="H86" s="70"/>
+      <c r="I86" s="70"/>
+      <c r="J86" s="70"/>
+      <c r="K86" s="70"/>
+      <c r="L86" s="70"/>
+      <c r="M86" s="70"/>
+      <c r="N86" s="70"/>
+      <c r="O86" s="70"/>
+      <c r="P86" s="70"/>
+      <c r="Q86" s="70"/>
+      <c r="R86" s="70"/>
+      <c r="S86" s="70"/>
+      <c r="T86" s="70"/>
+      <c r="U86" s="71"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="56"/>
+      <c r="A87" s="52"/>
       <c r="B87" s="32" t="s">
         <v>127</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D87" s="71"/>
-      <c r="E87" s="72"/>
-      <c r="F87" s="72"/>
-      <c r="G87" s="72"/>
-      <c r="H87" s="72"/>
-      <c r="I87" s="72"/>
-      <c r="J87" s="72"/>
-      <c r="K87" s="72"/>
-      <c r="L87" s="72"/>
-      <c r="M87" s="72"/>
-      <c r="N87" s="72"/>
-      <c r="O87" s="72"/>
-      <c r="P87" s="72"/>
-      <c r="Q87" s="72"/>
-      <c r="R87" s="72"/>
-      <c r="S87" s="72"/>
-      <c r="T87" s="72"/>
-      <c r="U87" s="73"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="70"/>
+      <c r="H87" s="70"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="70"/>
+      <c r="K87" s="70"/>
+      <c r="L87" s="70"/>
+      <c r="M87" s="70"/>
+      <c r="N87" s="70"/>
+      <c r="O87" s="70"/>
+      <c r="P87" s="70"/>
+      <c r="Q87" s="70"/>
+      <c r="R87" s="70"/>
+      <c r="S87" s="70"/>
+      <c r="T87" s="70"/>
+      <c r="U87" s="71"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="46">
+      <c r="A88" s="51">
         <v>13</v>
       </c>
       <c r="B88" s="34" t="s">
@@ -9805,189 +9798,189 @@
       <c r="C88" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="71"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="72"/>
-      <c r="G88" s="72"/>
-      <c r="H88" s="72"/>
-      <c r="I88" s="72"/>
-      <c r="J88" s="72"/>
-      <c r="K88" s="72"/>
-      <c r="L88" s="72"/>
-      <c r="M88" s="72"/>
-      <c r="N88" s="72"/>
-      <c r="O88" s="72"/>
-      <c r="P88" s="72"/>
-      <c r="Q88" s="72"/>
-      <c r="R88" s="72"/>
-      <c r="S88" s="72"/>
-      <c r="T88" s="72"/>
-      <c r="U88" s="73"/>
+      <c r="D88" s="69"/>
+      <c r="E88" s="70"/>
+      <c r="F88" s="70"/>
+      <c r="G88" s="70"/>
+      <c r="H88" s="70"/>
+      <c r="I88" s="70"/>
+      <c r="J88" s="70"/>
+      <c r="K88" s="70"/>
+      <c r="L88" s="70"/>
+      <c r="M88" s="70"/>
+      <c r="N88" s="70"/>
+      <c r="O88" s="70"/>
+      <c r="P88" s="70"/>
+      <c r="Q88" s="70"/>
+      <c r="R88" s="70"/>
+      <c r="S88" s="70"/>
+      <c r="T88" s="70"/>
+      <c r="U88" s="71"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="46"/>
+      <c r="A89" s="51"/>
       <c r="B89" s="34" t="s">
         <v>129</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D89" s="71"/>
-      <c r="E89" s="72"/>
-      <c r="F89" s="72"/>
-      <c r="G89" s="72"/>
-      <c r="H89" s="72"/>
-      <c r="I89" s="72"/>
-      <c r="J89" s="72"/>
-      <c r="K89" s="72"/>
-      <c r="L89" s="72"/>
-      <c r="M89" s="72"/>
-      <c r="N89" s="72"/>
-      <c r="O89" s="72"/>
-      <c r="P89" s="72"/>
-      <c r="Q89" s="72"/>
-      <c r="R89" s="72"/>
-      <c r="S89" s="72"/>
-      <c r="T89" s="72"/>
-      <c r="U89" s="73"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="70"/>
+      <c r="F89" s="70"/>
+      <c r="G89" s="70"/>
+      <c r="H89" s="70"/>
+      <c r="I89" s="70"/>
+      <c r="J89" s="70"/>
+      <c r="K89" s="70"/>
+      <c r="L89" s="70"/>
+      <c r="M89" s="70"/>
+      <c r="N89" s="70"/>
+      <c r="O89" s="70"/>
+      <c r="P89" s="70"/>
+      <c r="Q89" s="70"/>
+      <c r="R89" s="70"/>
+      <c r="S89" s="70"/>
+      <c r="T89" s="70"/>
+      <c r="U89" s="71"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="46"/>
+      <c r="A90" s="51"/>
       <c r="B90" s="34" t="s">
         <v>130</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D90" s="71"/>
-      <c r="E90" s="72"/>
-      <c r="F90" s="72"/>
-      <c r="G90" s="72"/>
-      <c r="H90" s="72"/>
-      <c r="I90" s="72"/>
-      <c r="J90" s="72"/>
-      <c r="K90" s="72"/>
-      <c r="L90" s="72"/>
-      <c r="M90" s="72"/>
-      <c r="N90" s="72"/>
-      <c r="O90" s="72"/>
-      <c r="P90" s="72"/>
-      <c r="Q90" s="72"/>
-      <c r="R90" s="72"/>
-      <c r="S90" s="72"/>
-      <c r="T90" s="72"/>
-      <c r="U90" s="73"/>
+      <c r="D90" s="69"/>
+      <c r="E90" s="70"/>
+      <c r="F90" s="70"/>
+      <c r="G90" s="70"/>
+      <c r="H90" s="70"/>
+      <c r="I90" s="70"/>
+      <c r="J90" s="70"/>
+      <c r="K90" s="70"/>
+      <c r="L90" s="70"/>
+      <c r="M90" s="70"/>
+      <c r="N90" s="70"/>
+      <c r="O90" s="70"/>
+      <c r="P90" s="70"/>
+      <c r="Q90" s="70"/>
+      <c r="R90" s="70"/>
+      <c r="S90" s="70"/>
+      <c r="T90" s="70"/>
+      <c r="U90" s="71"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="46"/>
+      <c r="A91" s="51"/>
       <c r="B91" s="34" t="s">
         <v>131</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D91" s="71"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
-      <c r="G91" s="72"/>
-      <c r="H91" s="72"/>
-      <c r="I91" s="72"/>
-      <c r="J91" s="72"/>
-      <c r="K91" s="72"/>
-      <c r="L91" s="72"/>
-      <c r="M91" s="72"/>
-      <c r="N91" s="72"/>
-      <c r="O91" s="72"/>
-      <c r="P91" s="72"/>
-      <c r="Q91" s="72"/>
-      <c r="R91" s="72"/>
-      <c r="S91" s="72"/>
-      <c r="T91" s="72"/>
-      <c r="U91" s="73"/>
+      <c r="D91" s="69"/>
+      <c r="E91" s="70"/>
+      <c r="F91" s="70"/>
+      <c r="G91" s="70"/>
+      <c r="H91" s="70"/>
+      <c r="I91" s="70"/>
+      <c r="J91" s="70"/>
+      <c r="K91" s="70"/>
+      <c r="L91" s="70"/>
+      <c r="M91" s="70"/>
+      <c r="N91" s="70"/>
+      <c r="O91" s="70"/>
+      <c r="P91" s="70"/>
+      <c r="Q91" s="70"/>
+      <c r="R91" s="70"/>
+      <c r="S91" s="70"/>
+      <c r="T91" s="70"/>
+      <c r="U91" s="71"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="46"/>
+      <c r="A92" s="51"/>
       <c r="B92" s="34" t="s">
         <v>132</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D92" s="71"/>
-      <c r="E92" s="72"/>
-      <c r="F92" s="72"/>
-      <c r="G92" s="72"/>
-      <c r="H92" s="72"/>
-      <c r="I92" s="72"/>
-      <c r="J92" s="72"/>
-      <c r="K92" s="72"/>
-      <c r="L92" s="72"/>
-      <c r="M92" s="72"/>
-      <c r="N92" s="72"/>
-      <c r="O92" s="72"/>
-      <c r="P92" s="72"/>
-      <c r="Q92" s="72"/>
-      <c r="R92" s="72"/>
-      <c r="S92" s="72"/>
-      <c r="T92" s="72"/>
-      <c r="U92" s="73"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="70"/>
+      <c r="F92" s="70"/>
+      <c r="G92" s="70"/>
+      <c r="H92" s="70"/>
+      <c r="I92" s="70"/>
+      <c r="J92" s="70"/>
+      <c r="K92" s="70"/>
+      <c r="L92" s="70"/>
+      <c r="M92" s="70"/>
+      <c r="N92" s="70"/>
+      <c r="O92" s="70"/>
+      <c r="P92" s="70"/>
+      <c r="Q92" s="70"/>
+      <c r="R92" s="70"/>
+      <c r="S92" s="70"/>
+      <c r="T92" s="70"/>
+      <c r="U92" s="71"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="46"/>
+      <c r="A93" s="51"/>
       <c r="B93" s="34" t="s">
         <v>133</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D93" s="71"/>
-      <c r="E93" s="72"/>
-      <c r="F93" s="72"/>
-      <c r="G93" s="72"/>
-      <c r="H93" s="72"/>
-      <c r="I93" s="72"/>
-      <c r="J93" s="72"/>
-      <c r="K93" s="72"/>
-      <c r="L93" s="72"/>
-      <c r="M93" s="72"/>
-      <c r="N93" s="72"/>
-      <c r="O93" s="72"/>
-      <c r="P93" s="72"/>
-      <c r="Q93" s="72"/>
-      <c r="R93" s="72"/>
-      <c r="S93" s="72"/>
-      <c r="T93" s="72"/>
-      <c r="U93" s="73"/>
+      <c r="D93" s="69"/>
+      <c r="E93" s="70"/>
+      <c r="F93" s="70"/>
+      <c r="G93" s="70"/>
+      <c r="H93" s="70"/>
+      <c r="I93" s="70"/>
+      <c r="J93" s="70"/>
+      <c r="K93" s="70"/>
+      <c r="L93" s="70"/>
+      <c r="M93" s="70"/>
+      <c r="N93" s="70"/>
+      <c r="O93" s="70"/>
+      <c r="P93" s="70"/>
+      <c r="Q93" s="70"/>
+      <c r="R93" s="70"/>
+      <c r="S93" s="70"/>
+      <c r="T93" s="70"/>
+      <c r="U93" s="71"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="46"/>
+      <c r="A94" s="51"/>
       <c r="B94" s="34" t="s">
         <v>134</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D94" s="74"/>
-      <c r="E94" s="75"/>
-      <c r="F94" s="75"/>
-      <c r="G94" s="75"/>
-      <c r="H94" s="75"/>
-      <c r="I94" s="75"/>
-      <c r="J94" s="75"/>
-      <c r="K94" s="75"/>
-      <c r="L94" s="75"/>
-      <c r="M94" s="75"/>
-      <c r="N94" s="75"/>
-      <c r="O94" s="75"/>
-      <c r="P94" s="75"/>
-      <c r="Q94" s="75"/>
-      <c r="R94" s="75"/>
-      <c r="S94" s="75"/>
-      <c r="T94" s="75"/>
-      <c r="U94" s="76"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="73"/>
+      <c r="F94" s="73"/>
+      <c r="G94" s="73"/>
+      <c r="H94" s="73"/>
+      <c r="I94" s="73"/>
+      <c r="J94" s="73"/>
+      <c r="K94" s="73"/>
+      <c r="L94" s="73"/>
+      <c r="M94" s="73"/>
+      <c r="N94" s="73"/>
+      <c r="O94" s="73"/>
+      <c r="P94" s="73"/>
+      <c r="Q94" s="73"/>
+      <c r="R94" s="73"/>
+      <c r="S94" s="73"/>
+      <c r="T94" s="73"/>
+      <c r="U94" s="74"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="56">
+      <c r="A95" s="52">
         <v>14</v>
       </c>
       <c r="B95" s="32" t="s">
@@ -10020,7 +10013,7 @@
       <c r="U95" s="18"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="56"/>
+      <c r="A96" s="52"/>
       <c r="B96" s="32" t="s">
         <v>137</v>
       </c>
@@ -10051,7 +10044,7 @@
       <c r="U96" s="18"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="56"/>
+      <c r="A97" s="52"/>
       <c r="B97" s="32" t="s">
         <v>138</v>
       </c>
@@ -10082,7 +10075,7 @@
       <c r="U97" s="18"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="56"/>
+      <c r="A98" s="52"/>
       <c r="B98" s="32" t="s">
         <v>139</v>
       </c>
@@ -10113,7 +10106,7 @@
       <c r="U98" s="18"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="56"/>
+      <c r="A99" s="52"/>
       <c r="B99" s="32" t="s">
         <v>140</v>
       </c>
@@ -10144,7 +10137,7 @@
       <c r="U99" s="18"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="56"/>
+      <c r="A100" s="52"/>
       <c r="B100" s="32" t="s">
         <v>141</v>
       </c>
@@ -10175,7 +10168,7 @@
       <c r="U100" s="18"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="56"/>
+      <c r="A101" s="52"/>
       <c r="B101" s="32" t="s">
         <v>142</v>
       </c>
@@ -10206,7 +10199,7 @@
       <c r="U101" s="18"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="46">
+      <c r="A102" s="51">
         <v>15</v>
       </c>
       <c r="B102" s="34" t="s">
@@ -10239,7 +10232,7 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="46"/>
+      <c r="A103" s="51"/>
       <c r="B103" s="34" t="s">
         <v>144</v>
       </c>
@@ -10270,7 +10263,7 @@
       <c r="U103" s="6"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="46"/>
+      <c r="A104" s="51"/>
       <c r="B104" s="34" t="s">
         <v>145</v>
       </c>
@@ -10301,7 +10294,7 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="46"/>
+      <c r="A105" s="51"/>
       <c r="B105" s="34" t="s">
         <v>146</v>
       </c>
@@ -10332,7 +10325,7 @@
       <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="46"/>
+      <c r="A106" s="51"/>
       <c r="B106" s="34" t="s">
         <v>147</v>
       </c>
@@ -10363,7 +10356,7 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="46"/>
+      <c r="A107" s="51"/>
       <c r="B107" s="34" t="s">
         <v>148</v>
       </c>
@@ -10394,7 +10387,7 @@
       <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="46"/>
+      <c r="A108" s="51"/>
       <c r="B108" s="34" t="s">
         <v>149</v>
       </c>
@@ -10425,7 +10418,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="56">
+      <c r="A109" s="52">
         <v>16</v>
       </c>
       <c r="B109" s="32" t="s">
@@ -10458,7 +10451,7 @@
       <c r="U109" s="17"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="56"/>
+      <c r="A110" s="52"/>
       <c r="B110" s="32" t="s">
         <v>151</v>
       </c>
@@ -10489,7 +10482,7 @@
       <c r="U110" s="17"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="56"/>
+      <c r="A111" s="52"/>
       <c r="B111" s="32" t="s">
         <v>152</v>
       </c>
@@ -10520,7 +10513,7 @@
       <c r="U111" s="17"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="56"/>
+      <c r="A112" s="52"/>
       <c r="B112" s="32" t="s">
         <v>153</v>
       </c>
@@ -10551,7 +10544,7 @@
       <c r="U112" s="17"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="56"/>
+      <c r="A113" s="52"/>
       <c r="B113" s="32" t="s">
         <v>154</v>
       </c>
@@ -10582,7 +10575,7 @@
       <c r="U113" s="17"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="56"/>
+      <c r="A114" s="52"/>
       <c r="B114" s="32" t="s">
         <v>155</v>
       </c>
@@ -10613,7 +10606,7 @@
       <c r="U114" s="17"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="56"/>
+      <c r="A115" s="52"/>
       <c r="B115" s="32" t="s">
         <v>156</v>
       </c>
@@ -10644,7 +10637,7 @@
       <c r="U115" s="17"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="46">
+      <c r="A116" s="51">
         <v>17</v>
       </c>
       <c r="B116" s="34" t="s">
@@ -10677,7 +10670,7 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="46"/>
+      <c r="A117" s="51"/>
       <c r="B117" s="34" t="s">
         <v>158</v>
       </c>
@@ -10708,7 +10701,7 @@
       <c r="U117" s="6"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="46"/>
+      <c r="A118" s="51"/>
       <c r="B118" s="34" t="s">
         <v>159</v>
       </c>
@@ -10739,7 +10732,7 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="46"/>
+      <c r="A119" s="51"/>
       <c r="B119" s="34" t="s">
         <v>160</v>
       </c>
@@ -10770,7 +10763,7 @@
       <c r="U119" s="6"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="46"/>
+      <c r="A120" s="51"/>
       <c r="B120" s="34" t="s">
         <v>161</v>
       </c>
@@ -10801,7 +10794,7 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="46"/>
+      <c r="A121" s="51"/>
       <c r="B121" s="34" t="s">
         <v>162</v>
       </c>
@@ -10832,7 +10825,7 @@
       <c r="U121" s="6"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="46"/>
+      <c r="A122" s="51"/>
       <c r="B122" s="34" t="s">
         <v>163</v>
       </c>
@@ -10863,7 +10856,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="56">
+      <c r="A123" s="52">
         <v>18</v>
       </c>
       <c r="B123" s="32" t="s">
@@ -10896,7 +10889,7 @@
       <c r="U123" s="17"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="56"/>
+      <c r="A124" s="52"/>
       <c r="B124" s="32" t="s">
         <v>165</v>
       </c>
@@ -10927,7 +10920,7 @@
       <c r="U124" s="17"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="56"/>
+      <c r="A125" s="52"/>
       <c r="B125" s="32" t="s">
         <v>166</v>
       </c>
@@ -10958,7 +10951,7 @@
       <c r="U125" s="17"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="56"/>
+      <c r="A126" s="52"/>
       <c r="B126" s="32" t="s">
         <v>167</v>
       </c>
@@ -10989,36 +10982,36 @@
       <c r="U126" s="17"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="56"/>
+      <c r="A127" s="52"/>
       <c r="B127" s="31" t="s">
         <v>168</v>
       </c>
       <c r="C127" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D127" s="65" t="s">
+      <c r="D127" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E127" s="66"/>
-      <c r="F127" s="66"/>
-      <c r="G127" s="66"/>
-      <c r="H127" s="66"/>
-      <c r="I127" s="66"/>
-      <c r="J127" s="66"/>
-      <c r="K127" s="66"/>
-      <c r="L127" s="66"/>
-      <c r="M127" s="66"/>
-      <c r="N127" s="66"/>
-      <c r="O127" s="66"/>
-      <c r="P127" s="66"/>
-      <c r="Q127" s="66"/>
-      <c r="R127" s="66"/>
-      <c r="S127" s="66"/>
-      <c r="T127" s="66"/>
-      <c r="U127" s="67"/>
+      <c r="E127" s="64"/>
+      <c r="F127" s="64"/>
+      <c r="G127" s="64"/>
+      <c r="H127" s="64"/>
+      <c r="I127" s="64"/>
+      <c r="J127" s="64"/>
+      <c r="K127" s="64"/>
+      <c r="L127" s="64"/>
+      <c r="M127" s="64"/>
+      <c r="N127" s="64"/>
+      <c r="O127" s="64"/>
+      <c r="P127" s="64"/>
+      <c r="Q127" s="64"/>
+      <c r="R127" s="64"/>
+      <c r="S127" s="64"/>
+      <c r="T127" s="64"/>
+      <c r="U127" s="65"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="56"/>
+      <c r="A128" s="52"/>
       <c r="B128" s="32" t="s">
         <v>169</v>
       </c>
@@ -11049,7 +11042,7 @@
       <c r="U128" s="17"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="56"/>
+      <c r="A129" s="52"/>
       <c r="B129" s="32" t="s">
         <v>170</v>
       </c>
@@ -11080,7 +11073,7 @@
       <c r="U129" s="17"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="46">
+      <c r="A130" s="51">
         <v>19</v>
       </c>
       <c r="B130" s="34" t="s">
@@ -11113,7 +11106,7 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="46"/>
+      <c r="A131" s="51"/>
       <c r="B131" s="34" t="s">
         <v>172</v>
       </c>
@@ -11144,7 +11137,7 @@
       <c r="U131" s="6"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="46"/>
+      <c r="A132" s="51"/>
       <c r="B132" s="34" t="s">
         <v>173</v>
       </c>
@@ -11175,7 +11168,7 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="46"/>
+      <c r="A133" s="51"/>
       <c r="B133" s="34" t="s">
         <v>174</v>
       </c>
@@ -11206,7 +11199,7 @@
       <c r="U133" s="6"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="46"/>
+      <c r="A134" s="51"/>
       <c r="B134" s="34" t="s">
         <v>175</v>
       </c>
@@ -11237,7 +11230,7 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="46"/>
+      <c r="A135" s="51"/>
       <c r="B135" s="34" t="s">
         <v>176</v>
       </c>
@@ -11268,7 +11261,7 @@
       <c r="U135" s="6"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="46"/>
+      <c r="A136" s="51"/>
       <c r="B136" s="34" t="s">
         <v>177</v>
       </c>
@@ -11314,6 +11307,32 @@
     <row r="150" ht="20.45"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="D29:U31"/>
+    <mergeCell ref="D35:U41"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="S2:U2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="A39:A45"/>
     <mergeCell ref="A74:A80"/>
     <mergeCell ref="A123:A129"/>
     <mergeCell ref="D127:U127"/>
@@ -11325,32 +11344,6 @@
     <mergeCell ref="A109:A115"/>
     <mergeCell ref="A116:A122"/>
     <mergeCell ref="A81:A87"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="A32:A38"/>
-    <mergeCell ref="D35:U41"/>
-    <mergeCell ref="A39:A45"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="S2:U2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11393,81 +11386,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="60" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60" t="s">
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60" t="s">
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60" t="s">
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60" t="s">
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="77" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="60" t="s">
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60" t="s">
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60" t="s">
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60" t="s">
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60" t="s">
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="46">
+      <c r="A4" s="51">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -11507,7 +11500,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="46"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
@@ -11571,7 +11564,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="46"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
@@ -11615,7 +11608,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="46"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
@@ -11661,7 +11654,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="46"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
@@ -11723,7 +11716,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="46"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
@@ -11767,7 +11760,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="46"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
@@ -11809,7 +11802,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="56">
+      <c r="A11" s="52">
         <v>2</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -11857,7 +11850,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="56"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="14" t="s">
         <v>47</v>
       </c>
@@ -11919,7 +11912,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="56"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="14" t="s">
         <v>50</v>
       </c>
@@ -11981,7 +11974,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="56"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="14" t="s">
         <v>51</v>
       </c>
@@ -12033,7 +12026,7 @@
       <c r="AA14" s="10"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="56"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="14" t="s">
         <v>52</v>
       </c>
@@ -12085,7 +12078,7 @@
       <c r="AA15" s="10"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="56"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="14" t="s">
         <v>53</v>
       </c>
@@ -12124,7 +12117,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="56"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="14" t="s">
         <v>55</v>
       </c>
@@ -12151,7 +12144,7 @@
       <c r="U17" s="18"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="46">
+      <c r="A18" s="51">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -12200,7 +12193,7 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="46"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -12247,7 +12240,7 @@
       <c r="U19" s="6"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="46"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -12294,7 +12287,7 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="46"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
@@ -12341,7 +12334,7 @@
       <c r="U21" s="6"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="46"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="2" t="s">
         <v>60</v>
       </c>
@@ -12388,7 +12381,7 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="46"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
@@ -12415,7 +12408,7 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="46"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="24" t="s">
         <v>62</v>
       </c>
@@ -12442,7 +12435,7 @@
       <c r="U24" s="28"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="56">
+      <c r="A25" s="52">
         <v>4</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -12491,7 +12484,7 @@
       <c r="U25" s="18"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="56"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="14" t="s">
         <v>64</v>
       </c>
@@ -12538,7 +12531,7 @@
       <c r="U26" s="18"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="56"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="14" t="s">
         <v>65</v>
       </c>
@@ -12585,7 +12578,7 @@
       <c r="U27" s="18"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="56"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="14" t="s">
         <v>66</v>
       </c>
@@ -12632,90 +12625,90 @@
       <c r="U28" s="18"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="56"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="29" t="s">
         <v>67</v>
       </c>
       <c r="C29" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="49"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="55"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="56"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="29" t="s">
         <v>69</v>
       </c>
       <c r="C30" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="50"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="51"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="52"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="58"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="56"/>
+      <c r="A31" s="52"/>
       <c r="B31" s="29" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="53"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="54"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="54"/>
-      <c r="R31" s="54"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="54"/>
-      <c r="U31" s="55"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="46">
+      <c r="A32" s="51">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -12746,7 +12739,7 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="46"/>
+      <c r="A33" s="51"/>
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
@@ -12793,7 +12786,7 @@
       <c r="U33" s="6"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="46"/>
+      <c r="A34" s="51"/>
       <c r="B34" s="2" t="s">
         <v>73</v>
       </c>
@@ -12840,117 +12833,117 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="46"/>
+      <c r="A35" s="51"/>
       <c r="B35" s="31" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="48"/>
-      <c r="R35" s="48"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="48"/>
-      <c r="U35" s="49"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="46"/>
+      <c r="A36" s="51"/>
       <c r="B36" s="31" t="s">
         <v>75</v>
       </c>
       <c r="C36" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="50"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="51"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="51"/>
-      <c r="S36" s="51"/>
-      <c r="T36" s="51"/>
-      <c r="U36" s="52"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="57"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="58"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="46"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="31" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="50"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="51"/>
-      <c r="M37" s="51"/>
-      <c r="N37" s="51"/>
-      <c r="O37" s="51"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="51"/>
-      <c r="S37" s="51"/>
-      <c r="T37" s="51"/>
-      <c r="U37" s="52"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="58"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="46"/>
+      <c r="A38" s="51"/>
       <c r="B38" s="31" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="51"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="51"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="51"/>
-      <c r="R38" s="51"/>
-      <c r="S38" s="51"/>
-      <c r="T38" s="51"/>
-      <c r="U38" s="52"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="58"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="56">
+      <c r="A39" s="52">
         <v>6</v>
       </c>
       <c r="B39" s="31" t="s">
@@ -12959,81 +12952,81 @@
       <c r="C39" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="50"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="51"/>
-      <c r="L39" s="51"/>
-      <c r="M39" s="51"/>
-      <c r="N39" s="51"/>
-      <c r="O39" s="51"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="51"/>
-      <c r="R39" s="51"/>
-      <c r="S39" s="51"/>
-      <c r="T39" s="51"/>
-      <c r="U39" s="52"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="58"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="56"/>
+      <c r="A40" s="52"/>
       <c r="B40" s="31" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="50"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="51"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="51"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="51"/>
-      <c r="R40" s="51"/>
-      <c r="S40" s="51"/>
-      <c r="T40" s="51"/>
-      <c r="U40" s="52"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
+      <c r="P40" s="57"/>
+      <c r="Q40" s="57"/>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="58"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="56"/>
+      <c r="A41" s="52"/>
       <c r="B41" s="31" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="53"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="54"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="54"/>
-      <c r="N41" s="54"/>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="54"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="55"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="61"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="56"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="32" t="s">
         <v>81</v>
       </c>
@@ -13080,7 +13073,7 @@
       <c r="U42" s="18"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="56"/>
+      <c r="A43" s="52"/>
       <c r="B43" s="32" t="s">
         <v>82</v>
       </c>
@@ -13127,7 +13120,7 @@
       <c r="U43" s="18"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="56"/>
+      <c r="A44" s="52"/>
       <c r="B44" s="33" t="s">
         <v>83</v>
       </c>
@@ -13154,7 +13147,7 @@
       <c r="U44" s="28"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="56"/>
+      <c r="A45" s="52"/>
       <c r="B45" s="32" t="s">
         <v>84</v>
       </c>
@@ -13181,7 +13174,7 @@
       <c r="U45" s="18"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="46">
+      <c r="A46" s="51">
         <v>7</v>
       </c>
       <c r="B46" s="34" t="s">
@@ -13230,7 +13223,7 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="46"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="34" t="s">
         <v>86</v>
       </c>
@@ -13277,7 +13270,7 @@
       <c r="U47" s="6"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="46"/>
+      <c r="A48" s="51"/>
       <c r="B48" s="34" t="s">
         <v>87</v>
       </c>
@@ -13324,7 +13317,7 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="46"/>
+      <c r="A49" s="51"/>
       <c r="B49" s="34" t="s">
         <v>88</v>
       </c>
@@ -13371,7 +13364,7 @@
       <c r="U49" s="6"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="46"/>
+      <c r="A50" s="51"/>
       <c r="B50" s="34" t="s">
         <v>89</v>
       </c>
@@ -13418,7 +13411,7 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="46"/>
+      <c r="A51" s="51"/>
       <c r="B51" s="34" t="s">
         <v>90</v>
       </c>
@@ -13445,7 +13438,7 @@
       <c r="U51" s="6"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="46"/>
+      <c r="A52" s="51"/>
       <c r="B52" s="34" t="s">
         <v>91</v>
       </c>
@@ -13472,7 +13465,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="56">
+      <c r="A53" s="52">
         <v>8</v>
       </c>
       <c r="B53" s="32" t="s">
@@ -13503,7 +13496,7 @@
       <c r="U53" s="18"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="56"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="32" t="s">
         <v>93</v>
       </c>
@@ -13550,7 +13543,7 @@
       <c r="U54" s="18"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="56"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="32" t="s">
         <v>94</v>
       </c>
@@ -13597,7 +13590,7 @@
       <c r="U55" s="18"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="56"/>
+      <c r="A56" s="52"/>
       <c r="B56" s="32" t="s">
         <v>95</v>
       </c>
@@ -13644,7 +13637,7 @@
       <c r="U56" s="18"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="56"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="32" t="s">
         <v>96</v>
       </c>
@@ -13691,7 +13684,7 @@
       <c r="U57" s="18"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="56"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="32" t="s">
         <v>97</v>
       </c>
@@ -13718,7 +13711,7 @@
       <c r="U58" s="18"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="56"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="32" t="s">
         <v>98</v>
       </c>
@@ -13745,7 +13738,7 @@
       <c r="U59" s="18"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="46">
+      <c r="A60" s="51">
         <v>9</v>
       </c>
       <c r="B60" s="34" t="s">
@@ -13776,7 +13769,7 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="46"/>
+      <c r="A61" s="51"/>
       <c r="B61" s="34" t="s">
         <v>100</v>
       </c>
@@ -13823,7 +13816,7 @@
       <c r="U61" s="6"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="46"/>
+      <c r="A62" s="51"/>
       <c r="B62" s="34" t="s">
         <v>101</v>
       </c>
@@ -13870,7 +13863,7 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="46"/>
+      <c r="A63" s="51"/>
       <c r="B63" s="34" t="s">
         <v>102</v>
       </c>
@@ -13917,7 +13910,7 @@
       <c r="U63" s="5"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="46"/>
+      <c r="A64" s="51"/>
       <c r="B64" s="34" t="s">
         <v>103</v>
       </c>
@@ -13964,7 +13957,7 @@
       <c r="U64" s="5"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="46"/>
+      <c r="A65" s="51"/>
       <c r="B65" s="34" t="s">
         <v>104</v>
       </c>
@@ -13991,7 +13984,7 @@
       <c r="U65" s="5"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="46"/>
+      <c r="A66" s="51"/>
       <c r="B66" s="34" t="s">
         <v>105</v>
       </c>
@@ -14018,7 +14011,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="56">
+      <c r="A67" s="52">
         <v>10</v>
       </c>
       <c r="B67" s="32" t="s">
@@ -14049,7 +14042,7 @@
       <c r="U67" s="17"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="56"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="32" t="s">
         <v>107</v>
       </c>
@@ -14096,7 +14089,7 @@
       <c r="U68" s="17"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="56"/>
+      <c r="A69" s="52"/>
       <c r="B69" s="32" t="s">
         <v>108</v>
       </c>
@@ -14143,7 +14136,7 @@
       <c r="U69" s="17"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="56"/>
+      <c r="A70" s="52"/>
       <c r="B70" s="32" t="s">
         <v>109</v>
       </c>
@@ -14190,7 +14183,7 @@
       <c r="U70" s="17"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="56"/>
+      <c r="A71" s="52"/>
       <c r="B71" s="32" t="s">
         <v>110</v>
       </c>
@@ -14237,7 +14230,7 @@
       <c r="U71" s="17"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="56"/>
+      <c r="A72" s="52"/>
       <c r="B72" s="32" t="s">
         <v>111</v>
       </c>
@@ -14264,7 +14257,7 @@
       <c r="U72" s="17"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="56"/>
+      <c r="A73" s="52"/>
       <c r="B73" s="32" t="s">
         <v>112</v>
       </c>
@@ -14291,7 +14284,7 @@
       <c r="U73" s="17"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="46">
+      <c r="A74" s="51">
         <v>11</v>
       </c>
       <c r="B74" s="34" t="s">
@@ -14322,7 +14315,7 @@
       <c r="U74" s="5"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="46"/>
+      <c r="A75" s="51"/>
       <c r="B75" s="34" t="s">
         <v>114</v>
       </c>
@@ -14369,7 +14362,7 @@
       <c r="U75" s="5"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="46"/>
+      <c r="A76" s="51"/>
       <c r="B76" s="34" t="s">
         <v>115</v>
       </c>
@@ -14416,7 +14409,7 @@
       <c r="U76" s="5"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="46"/>
+      <c r="A77" s="51"/>
       <c r="B77" s="34" t="s">
         <v>116</v>
       </c>
@@ -14463,7 +14456,7 @@
       <c r="U77" s="6"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="46"/>
+      <c r="A78" s="51"/>
       <c r="B78" s="34" t="s">
         <v>117</v>
       </c>
@@ -14510,7 +14503,7 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="46"/>
+      <c r="A79" s="51"/>
       <c r="B79" s="34" t="s">
         <v>118</v>
       </c>
@@ -14537,7 +14530,7 @@
       <c r="U79" s="6"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="46"/>
+      <c r="A80" s="51"/>
       <c r="B80" s="34" t="s">
         <v>119</v>
       </c>
@@ -14564,7 +14557,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="56">
+      <c r="A81" s="52">
         <v>12</v>
       </c>
       <c r="B81" s="32" t="s">
@@ -14573,191 +14566,191 @@
       <c r="C81" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="68" t="s">
+      <c r="D81" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="E81" s="69"/>
-      <c r="F81" s="69"/>
-      <c r="G81" s="69"/>
-      <c r="H81" s="69"/>
-      <c r="I81" s="69"/>
-      <c r="J81" s="69"/>
-      <c r="K81" s="69"/>
-      <c r="L81" s="69"/>
-      <c r="M81" s="69"/>
-      <c r="N81" s="69"/>
-      <c r="O81" s="69"/>
-      <c r="P81" s="69"/>
-      <c r="Q81" s="69"/>
-      <c r="R81" s="69"/>
-      <c r="S81" s="69"/>
-      <c r="T81" s="69"/>
-      <c r="U81" s="70"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="67"/>
+      <c r="H81" s="67"/>
+      <c r="I81" s="67"/>
+      <c r="J81" s="67"/>
+      <c r="K81" s="67"/>
+      <c r="L81" s="67"/>
+      <c r="M81" s="67"/>
+      <c r="N81" s="67"/>
+      <c r="O81" s="67"/>
+      <c r="P81" s="67"/>
+      <c r="Q81" s="67"/>
+      <c r="R81" s="67"/>
+      <c r="S81" s="67"/>
+      <c r="T81" s="67"/>
+      <c r="U81" s="68"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="56"/>
+      <c r="A82" s="52"/>
       <c r="B82" s="32" t="s">
         <v>122</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="71"/>
-      <c r="E82" s="72"/>
-      <c r="F82" s="72"/>
-      <c r="G82" s="72"/>
-      <c r="H82" s="72"/>
-      <c r="I82" s="72"/>
-      <c r="J82" s="72"/>
-      <c r="K82" s="72"/>
-      <c r="L82" s="72"/>
-      <c r="M82" s="72"/>
-      <c r="N82" s="72"/>
-      <c r="O82" s="72"/>
-      <c r="P82" s="72"/>
-      <c r="Q82" s="72"/>
-      <c r="R82" s="72"/>
-      <c r="S82" s="72"/>
-      <c r="T82" s="72"/>
-      <c r="U82" s="73"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="70"/>
+      <c r="I82" s="70"/>
+      <c r="J82" s="70"/>
+      <c r="K82" s="70"/>
+      <c r="L82" s="70"/>
+      <c r="M82" s="70"/>
+      <c r="N82" s="70"/>
+      <c r="O82" s="70"/>
+      <c r="P82" s="70"/>
+      <c r="Q82" s="70"/>
+      <c r="R82" s="70"/>
+      <c r="S82" s="70"/>
+      <c r="T82" s="70"/>
+      <c r="U82" s="71"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="56"/>
+      <c r="A83" s="52"/>
       <c r="B83" s="32" t="s">
         <v>123</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D83" s="71"/>
-      <c r="E83" s="72"/>
-      <c r="F83" s="72"/>
-      <c r="G83" s="72"/>
-      <c r="H83" s="72"/>
-      <c r="I83" s="72"/>
-      <c r="J83" s="72"/>
-      <c r="K83" s="72"/>
-      <c r="L83" s="72"/>
-      <c r="M83" s="72"/>
-      <c r="N83" s="72"/>
-      <c r="O83" s="72"/>
-      <c r="P83" s="72"/>
-      <c r="Q83" s="72"/>
-      <c r="R83" s="72"/>
-      <c r="S83" s="72"/>
-      <c r="T83" s="72"/>
-      <c r="U83" s="73"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="70"/>
+      <c r="G83" s="70"/>
+      <c r="H83" s="70"/>
+      <c r="I83" s="70"/>
+      <c r="J83" s="70"/>
+      <c r="K83" s="70"/>
+      <c r="L83" s="70"/>
+      <c r="M83" s="70"/>
+      <c r="N83" s="70"/>
+      <c r="O83" s="70"/>
+      <c r="P83" s="70"/>
+      <c r="Q83" s="70"/>
+      <c r="R83" s="70"/>
+      <c r="S83" s="70"/>
+      <c r="T83" s="70"/>
+      <c r="U83" s="71"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="56"/>
+      <c r="A84" s="52"/>
       <c r="B84" s="32" t="s">
         <v>124</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D84" s="71"/>
-      <c r="E84" s="72"/>
-      <c r="F84" s="72"/>
-      <c r="G84" s="72"/>
-      <c r="H84" s="72"/>
-      <c r="I84" s="72"/>
-      <c r="J84" s="72"/>
-      <c r="K84" s="72"/>
-      <c r="L84" s="72"/>
-      <c r="M84" s="72"/>
-      <c r="N84" s="72"/>
-      <c r="O84" s="72"/>
-      <c r="P84" s="72"/>
-      <c r="Q84" s="72"/>
-      <c r="R84" s="72"/>
-      <c r="S84" s="72"/>
-      <c r="T84" s="72"/>
-      <c r="U84" s="73"/>
+      <c r="D84" s="69"/>
+      <c r="E84" s="70"/>
+      <c r="F84" s="70"/>
+      <c r="G84" s="70"/>
+      <c r="H84" s="70"/>
+      <c r="I84" s="70"/>
+      <c r="J84" s="70"/>
+      <c r="K84" s="70"/>
+      <c r="L84" s="70"/>
+      <c r="M84" s="70"/>
+      <c r="N84" s="70"/>
+      <c r="O84" s="70"/>
+      <c r="P84" s="70"/>
+      <c r="Q84" s="70"/>
+      <c r="R84" s="70"/>
+      <c r="S84" s="70"/>
+      <c r="T84" s="70"/>
+      <c r="U84" s="71"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="56"/>
+      <c r="A85" s="52"/>
       <c r="B85" s="32" t="s">
         <v>125</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D85" s="71"/>
-      <c r="E85" s="72"/>
-      <c r="F85" s="72"/>
-      <c r="G85" s="72"/>
-      <c r="H85" s="72"/>
-      <c r="I85" s="72"/>
-      <c r="J85" s="72"/>
-      <c r="K85" s="72"/>
-      <c r="L85" s="72"/>
-      <c r="M85" s="72"/>
-      <c r="N85" s="72"/>
-      <c r="O85" s="72"/>
-      <c r="P85" s="72"/>
-      <c r="Q85" s="72"/>
-      <c r="R85" s="72"/>
-      <c r="S85" s="72"/>
-      <c r="T85" s="72"/>
-      <c r="U85" s="73"/>
+      <c r="D85" s="69"/>
+      <c r="E85" s="70"/>
+      <c r="F85" s="70"/>
+      <c r="G85" s="70"/>
+      <c r="H85" s="70"/>
+      <c r="I85" s="70"/>
+      <c r="J85" s="70"/>
+      <c r="K85" s="70"/>
+      <c r="L85" s="70"/>
+      <c r="M85" s="70"/>
+      <c r="N85" s="70"/>
+      <c r="O85" s="70"/>
+      <c r="P85" s="70"/>
+      <c r="Q85" s="70"/>
+      <c r="R85" s="70"/>
+      <c r="S85" s="70"/>
+      <c r="T85" s="70"/>
+      <c r="U85" s="71"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="56"/>
+      <c r="A86" s="52"/>
       <c r="B86" s="32" t="s">
         <v>126</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D86" s="71"/>
-      <c r="E86" s="72"/>
-      <c r="F86" s="72"/>
-      <c r="G86" s="72"/>
-      <c r="H86" s="72"/>
-      <c r="I86" s="72"/>
-      <c r="J86" s="72"/>
-      <c r="K86" s="72"/>
-      <c r="L86" s="72"/>
-      <c r="M86" s="72"/>
-      <c r="N86" s="72"/>
-      <c r="O86" s="72"/>
-      <c r="P86" s="72"/>
-      <c r="Q86" s="72"/>
-      <c r="R86" s="72"/>
-      <c r="S86" s="72"/>
-      <c r="T86" s="72"/>
-      <c r="U86" s="73"/>
+      <c r="D86" s="69"/>
+      <c r="E86" s="70"/>
+      <c r="F86" s="70"/>
+      <c r="G86" s="70"/>
+      <c r="H86" s="70"/>
+      <c r="I86" s="70"/>
+      <c r="J86" s="70"/>
+      <c r="K86" s="70"/>
+      <c r="L86" s="70"/>
+      <c r="M86" s="70"/>
+      <c r="N86" s="70"/>
+      <c r="O86" s="70"/>
+      <c r="P86" s="70"/>
+      <c r="Q86" s="70"/>
+      <c r="R86" s="70"/>
+      <c r="S86" s="70"/>
+      <c r="T86" s="70"/>
+      <c r="U86" s="71"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="56"/>
+      <c r="A87" s="52"/>
       <c r="B87" s="32" t="s">
         <v>127</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D87" s="71"/>
-      <c r="E87" s="72"/>
-      <c r="F87" s="72"/>
-      <c r="G87" s="72"/>
-      <c r="H87" s="72"/>
-      <c r="I87" s="72"/>
-      <c r="J87" s="72"/>
-      <c r="K87" s="72"/>
-      <c r="L87" s="72"/>
-      <c r="M87" s="72"/>
-      <c r="N87" s="72"/>
-      <c r="O87" s="72"/>
-      <c r="P87" s="72"/>
-      <c r="Q87" s="72"/>
-      <c r="R87" s="72"/>
-      <c r="S87" s="72"/>
-      <c r="T87" s="72"/>
-      <c r="U87" s="73"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="70"/>
+      <c r="H87" s="70"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="70"/>
+      <c r="K87" s="70"/>
+      <c r="L87" s="70"/>
+      <c r="M87" s="70"/>
+      <c r="N87" s="70"/>
+      <c r="O87" s="70"/>
+      <c r="P87" s="70"/>
+      <c r="Q87" s="70"/>
+      <c r="R87" s="70"/>
+      <c r="S87" s="70"/>
+      <c r="T87" s="70"/>
+      <c r="U87" s="71"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="46">
+      <c r="A88" s="51">
         <v>13</v>
       </c>
       <c r="B88" s="34" t="s">
@@ -14766,189 +14759,189 @@
       <c r="C88" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="71"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="72"/>
-      <c r="G88" s="72"/>
-      <c r="H88" s="72"/>
-      <c r="I88" s="72"/>
-      <c r="J88" s="72"/>
-      <c r="K88" s="72"/>
-      <c r="L88" s="72"/>
-      <c r="M88" s="72"/>
-      <c r="N88" s="72"/>
-      <c r="O88" s="72"/>
-      <c r="P88" s="72"/>
-      <c r="Q88" s="72"/>
-      <c r="R88" s="72"/>
-      <c r="S88" s="72"/>
-      <c r="T88" s="72"/>
-      <c r="U88" s="73"/>
+      <c r="D88" s="69"/>
+      <c r="E88" s="70"/>
+      <c r="F88" s="70"/>
+      <c r="G88" s="70"/>
+      <c r="H88" s="70"/>
+      <c r="I88" s="70"/>
+      <c r="J88" s="70"/>
+      <c r="K88" s="70"/>
+      <c r="L88" s="70"/>
+      <c r="M88" s="70"/>
+      <c r="N88" s="70"/>
+      <c r="O88" s="70"/>
+      <c r="P88" s="70"/>
+      <c r="Q88" s="70"/>
+      <c r="R88" s="70"/>
+      <c r="S88" s="70"/>
+      <c r="T88" s="70"/>
+      <c r="U88" s="71"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="46"/>
+      <c r="A89" s="51"/>
       <c r="B89" s="34" t="s">
         <v>129</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D89" s="71"/>
-      <c r="E89" s="72"/>
-      <c r="F89" s="72"/>
-      <c r="G89" s="72"/>
-      <c r="H89" s="72"/>
-      <c r="I89" s="72"/>
-      <c r="J89" s="72"/>
-      <c r="K89" s="72"/>
-      <c r="L89" s="72"/>
-      <c r="M89" s="72"/>
-      <c r="N89" s="72"/>
-      <c r="O89" s="72"/>
-      <c r="P89" s="72"/>
-      <c r="Q89" s="72"/>
-      <c r="R89" s="72"/>
-      <c r="S89" s="72"/>
-      <c r="T89" s="72"/>
-      <c r="U89" s="73"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="70"/>
+      <c r="F89" s="70"/>
+      <c r="G89" s="70"/>
+      <c r="H89" s="70"/>
+      <c r="I89" s="70"/>
+      <c r="J89" s="70"/>
+      <c r="K89" s="70"/>
+      <c r="L89" s="70"/>
+      <c r="M89" s="70"/>
+      <c r="N89" s="70"/>
+      <c r="O89" s="70"/>
+      <c r="P89" s="70"/>
+      <c r="Q89" s="70"/>
+      <c r="R89" s="70"/>
+      <c r="S89" s="70"/>
+      <c r="T89" s="70"/>
+      <c r="U89" s="71"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="46"/>
+      <c r="A90" s="51"/>
       <c r="B90" s="34" t="s">
         <v>130</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D90" s="71"/>
-      <c r="E90" s="72"/>
-      <c r="F90" s="72"/>
-      <c r="G90" s="72"/>
-      <c r="H90" s="72"/>
-      <c r="I90" s="72"/>
-      <c r="J90" s="72"/>
-      <c r="K90" s="72"/>
-      <c r="L90" s="72"/>
-      <c r="M90" s="72"/>
-      <c r="N90" s="72"/>
-      <c r="O90" s="72"/>
-      <c r="P90" s="72"/>
-      <c r="Q90" s="72"/>
-      <c r="R90" s="72"/>
-      <c r="S90" s="72"/>
-      <c r="T90" s="72"/>
-      <c r="U90" s="73"/>
+      <c r="D90" s="69"/>
+      <c r="E90" s="70"/>
+      <c r="F90" s="70"/>
+      <c r="G90" s="70"/>
+      <c r="H90" s="70"/>
+      <c r="I90" s="70"/>
+      <c r="J90" s="70"/>
+      <c r="K90" s="70"/>
+      <c r="L90" s="70"/>
+      <c r="M90" s="70"/>
+      <c r="N90" s="70"/>
+      <c r="O90" s="70"/>
+      <c r="P90" s="70"/>
+      <c r="Q90" s="70"/>
+      <c r="R90" s="70"/>
+      <c r="S90" s="70"/>
+      <c r="T90" s="70"/>
+      <c r="U90" s="71"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="46"/>
+      <c r="A91" s="51"/>
       <c r="B91" s="34" t="s">
         <v>131</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D91" s="71"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
-      <c r="G91" s="72"/>
-      <c r="H91" s="72"/>
-      <c r="I91" s="72"/>
-      <c r="J91" s="72"/>
-      <c r="K91" s="72"/>
-      <c r="L91" s="72"/>
-      <c r="M91" s="72"/>
-      <c r="N91" s="72"/>
-      <c r="O91" s="72"/>
-      <c r="P91" s="72"/>
-      <c r="Q91" s="72"/>
-      <c r="R91" s="72"/>
-      <c r="S91" s="72"/>
-      <c r="T91" s="72"/>
-      <c r="U91" s="73"/>
+      <c r="D91" s="69"/>
+      <c r="E91" s="70"/>
+      <c r="F91" s="70"/>
+      <c r="G91" s="70"/>
+      <c r="H91" s="70"/>
+      <c r="I91" s="70"/>
+      <c r="J91" s="70"/>
+      <c r="K91" s="70"/>
+      <c r="L91" s="70"/>
+      <c r="M91" s="70"/>
+      <c r="N91" s="70"/>
+      <c r="O91" s="70"/>
+      <c r="P91" s="70"/>
+      <c r="Q91" s="70"/>
+      <c r="R91" s="70"/>
+      <c r="S91" s="70"/>
+      <c r="T91" s="70"/>
+      <c r="U91" s="71"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="46"/>
+      <c r="A92" s="51"/>
       <c r="B92" s="34" t="s">
         <v>132</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D92" s="71"/>
-      <c r="E92" s="72"/>
-      <c r="F92" s="72"/>
-      <c r="G92" s="72"/>
-      <c r="H92" s="72"/>
-      <c r="I92" s="72"/>
-      <c r="J92" s="72"/>
-      <c r="K92" s="72"/>
-      <c r="L92" s="72"/>
-      <c r="M92" s="72"/>
-      <c r="N92" s="72"/>
-      <c r="O92" s="72"/>
-      <c r="P92" s="72"/>
-      <c r="Q92" s="72"/>
-      <c r="R92" s="72"/>
-      <c r="S92" s="72"/>
-      <c r="T92" s="72"/>
-      <c r="U92" s="73"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="70"/>
+      <c r="F92" s="70"/>
+      <c r="G92" s="70"/>
+      <c r="H92" s="70"/>
+      <c r="I92" s="70"/>
+      <c r="J92" s="70"/>
+      <c r="K92" s="70"/>
+      <c r="L92" s="70"/>
+      <c r="M92" s="70"/>
+      <c r="N92" s="70"/>
+      <c r="O92" s="70"/>
+      <c r="P92" s="70"/>
+      <c r="Q92" s="70"/>
+      <c r="R92" s="70"/>
+      <c r="S92" s="70"/>
+      <c r="T92" s="70"/>
+      <c r="U92" s="71"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="46"/>
+      <c r="A93" s="51"/>
       <c r="B93" s="34" t="s">
         <v>133</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D93" s="71"/>
-      <c r="E93" s="72"/>
-      <c r="F93" s="72"/>
-      <c r="G93" s="72"/>
-      <c r="H93" s="72"/>
-      <c r="I93" s="72"/>
-      <c r="J93" s="72"/>
-      <c r="K93" s="72"/>
-      <c r="L93" s="72"/>
-      <c r="M93" s="72"/>
-      <c r="N93" s="72"/>
-      <c r="O93" s="72"/>
-      <c r="P93" s="72"/>
-      <c r="Q93" s="72"/>
-      <c r="R93" s="72"/>
-      <c r="S93" s="72"/>
-      <c r="T93" s="72"/>
-      <c r="U93" s="73"/>
+      <c r="D93" s="69"/>
+      <c r="E93" s="70"/>
+      <c r="F93" s="70"/>
+      <c r="G93" s="70"/>
+      <c r="H93" s="70"/>
+      <c r="I93" s="70"/>
+      <c r="J93" s="70"/>
+      <c r="K93" s="70"/>
+      <c r="L93" s="70"/>
+      <c r="M93" s="70"/>
+      <c r="N93" s="70"/>
+      <c r="O93" s="70"/>
+      <c r="P93" s="70"/>
+      <c r="Q93" s="70"/>
+      <c r="R93" s="70"/>
+      <c r="S93" s="70"/>
+      <c r="T93" s="70"/>
+      <c r="U93" s="71"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="46"/>
+      <c r="A94" s="51"/>
       <c r="B94" s="34" t="s">
         <v>134</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D94" s="74"/>
-      <c r="E94" s="75"/>
-      <c r="F94" s="75"/>
-      <c r="G94" s="75"/>
-      <c r="H94" s="75"/>
-      <c r="I94" s="75"/>
-      <c r="J94" s="75"/>
-      <c r="K94" s="75"/>
-      <c r="L94" s="75"/>
-      <c r="M94" s="75"/>
-      <c r="N94" s="75"/>
-      <c r="O94" s="75"/>
-      <c r="P94" s="75"/>
-      <c r="Q94" s="75"/>
-      <c r="R94" s="75"/>
-      <c r="S94" s="75"/>
-      <c r="T94" s="75"/>
-      <c r="U94" s="76"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="73"/>
+      <c r="F94" s="73"/>
+      <c r="G94" s="73"/>
+      <c r="H94" s="73"/>
+      <c r="I94" s="73"/>
+      <c r="J94" s="73"/>
+      <c r="K94" s="73"/>
+      <c r="L94" s="73"/>
+      <c r="M94" s="73"/>
+      <c r="N94" s="73"/>
+      <c r="O94" s="73"/>
+      <c r="P94" s="73"/>
+      <c r="Q94" s="73"/>
+      <c r="R94" s="73"/>
+      <c r="S94" s="73"/>
+      <c r="T94" s="73"/>
+      <c r="U94" s="74"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="56">
+      <c r="A95" s="52">
         <v>14</v>
       </c>
       <c r="B95" s="32" t="s">
@@ -14981,7 +14974,7 @@
       <c r="U95" s="18"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="56"/>
+      <c r="A96" s="52"/>
       <c r="B96" s="32" t="s">
         <v>137</v>
       </c>
@@ -15012,7 +15005,7 @@
       <c r="U96" s="18"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="56"/>
+      <c r="A97" s="52"/>
       <c r="B97" s="32" t="s">
         <v>138</v>
       </c>
@@ -15043,7 +15036,7 @@
       <c r="U97" s="18"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="56"/>
+      <c r="A98" s="52"/>
       <c r="B98" s="32" t="s">
         <v>139</v>
       </c>
@@ -15074,7 +15067,7 @@
       <c r="U98" s="18"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="56"/>
+      <c r="A99" s="52"/>
       <c r="B99" s="32" t="s">
         <v>140</v>
       </c>
@@ -15105,7 +15098,7 @@
       <c r="U99" s="18"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="56"/>
+      <c r="A100" s="52"/>
       <c r="B100" s="32" t="s">
         <v>141</v>
       </c>
@@ -15136,7 +15129,7 @@
       <c r="U100" s="18"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="56"/>
+      <c r="A101" s="52"/>
       <c r="B101" s="32" t="s">
         <v>142</v>
       </c>
@@ -15167,7 +15160,7 @@
       <c r="U101" s="18"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="46">
+      <c r="A102" s="51">
         <v>15</v>
       </c>
       <c r="B102" s="34" t="s">
@@ -15200,7 +15193,7 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="46"/>
+      <c r="A103" s="51"/>
       <c r="B103" s="34" t="s">
         <v>144</v>
       </c>
@@ -15231,7 +15224,7 @@
       <c r="U103" s="6"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="46"/>
+      <c r="A104" s="51"/>
       <c r="B104" s="34" t="s">
         <v>145</v>
       </c>
@@ -15262,7 +15255,7 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="46"/>
+      <c r="A105" s="51"/>
       <c r="B105" s="34" t="s">
         <v>146</v>
       </c>
@@ -15293,7 +15286,7 @@
       <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="46"/>
+      <c r="A106" s="51"/>
       <c r="B106" s="34" t="s">
         <v>147</v>
       </c>
@@ -15324,7 +15317,7 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="46"/>
+      <c r="A107" s="51"/>
       <c r="B107" s="34" t="s">
         <v>148</v>
       </c>
@@ -15355,7 +15348,7 @@
       <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="46"/>
+      <c r="A108" s="51"/>
       <c r="B108" s="34" t="s">
         <v>149</v>
       </c>
@@ -15386,7 +15379,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="56">
+      <c r="A109" s="52">
         <v>16</v>
       </c>
       <c r="B109" s="32" t="s">
@@ -15419,7 +15412,7 @@
       <c r="U109" s="17"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="56"/>
+      <c r="A110" s="52"/>
       <c r="B110" s="32" t="s">
         <v>151</v>
       </c>
@@ -15450,7 +15443,7 @@
       <c r="U110" s="17"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="56"/>
+      <c r="A111" s="52"/>
       <c r="B111" s="32" t="s">
         <v>152</v>
       </c>
@@ -15481,7 +15474,7 @@
       <c r="U111" s="17"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="56"/>
+      <c r="A112" s="52"/>
       <c r="B112" s="32" t="s">
         <v>153</v>
       </c>
@@ -15512,7 +15505,7 @@
       <c r="U112" s="17"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="56"/>
+      <c r="A113" s="52"/>
       <c r="B113" s="32" t="s">
         <v>154</v>
       </c>
@@ -15543,7 +15536,7 @@
       <c r="U113" s="17"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="56"/>
+      <c r="A114" s="52"/>
       <c r="B114" s="32" t="s">
         <v>155</v>
       </c>
@@ -15574,7 +15567,7 @@
       <c r="U114" s="17"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="56"/>
+      <c r="A115" s="52"/>
       <c r="B115" s="32" t="s">
         <v>156</v>
       </c>
@@ -15605,7 +15598,7 @@
       <c r="U115" s="17"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="46">
+      <c r="A116" s="51">
         <v>17</v>
       </c>
       <c r="B116" s="34" t="s">
@@ -15638,7 +15631,7 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="46"/>
+      <c r="A117" s="51"/>
       <c r="B117" s="34" t="s">
         <v>158</v>
       </c>
@@ -15669,7 +15662,7 @@
       <c r="U117" s="6"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="46"/>
+      <c r="A118" s="51"/>
       <c r="B118" s="34" t="s">
         <v>159</v>
       </c>
@@ -15700,7 +15693,7 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="46"/>
+      <c r="A119" s="51"/>
       <c r="B119" s="34" t="s">
         <v>160</v>
       </c>
@@ -15731,7 +15724,7 @@
       <c r="U119" s="6"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="46"/>
+      <c r="A120" s="51"/>
       <c r="B120" s="34" t="s">
         <v>161</v>
       </c>
@@ -15762,7 +15755,7 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="46"/>
+      <c r="A121" s="51"/>
       <c r="B121" s="34" t="s">
         <v>162</v>
       </c>
@@ -15793,7 +15786,7 @@
       <c r="U121" s="6"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="46"/>
+      <c r="A122" s="51"/>
       <c r="B122" s="34" t="s">
         <v>163</v>
       </c>
@@ -15824,7 +15817,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="56">
+      <c r="A123" s="52">
         <v>18</v>
       </c>
       <c r="B123" s="32" t="s">
@@ -15857,7 +15850,7 @@
       <c r="U123" s="17"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="56"/>
+      <c r="A124" s="52"/>
       <c r="B124" s="32" t="s">
         <v>165</v>
       </c>
@@ -15888,7 +15881,7 @@
       <c r="U124" s="17"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="56"/>
+      <c r="A125" s="52"/>
       <c r="B125" s="32" t="s">
         <v>166</v>
       </c>
@@ -15919,7 +15912,7 @@
       <c r="U125" s="17"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="56"/>
+      <c r="A126" s="52"/>
       <c r="B126" s="32" t="s">
         <v>167</v>
       </c>
@@ -15950,36 +15943,36 @@
       <c r="U126" s="17"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="56"/>
+      <c r="A127" s="52"/>
       <c r="B127" s="31" t="s">
         <v>168</v>
       </c>
       <c r="C127" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D127" s="65" t="s">
+      <c r="D127" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E127" s="66"/>
-      <c r="F127" s="66"/>
-      <c r="G127" s="66"/>
-      <c r="H127" s="66"/>
-      <c r="I127" s="66"/>
-      <c r="J127" s="66"/>
-      <c r="K127" s="66"/>
-      <c r="L127" s="66"/>
-      <c r="M127" s="66"/>
-      <c r="N127" s="66"/>
-      <c r="O127" s="66"/>
-      <c r="P127" s="66"/>
-      <c r="Q127" s="66"/>
-      <c r="R127" s="66"/>
-      <c r="S127" s="66"/>
-      <c r="T127" s="66"/>
-      <c r="U127" s="67"/>
+      <c r="E127" s="64"/>
+      <c r="F127" s="64"/>
+      <c r="G127" s="64"/>
+      <c r="H127" s="64"/>
+      <c r="I127" s="64"/>
+      <c r="J127" s="64"/>
+      <c r="K127" s="64"/>
+      <c r="L127" s="64"/>
+      <c r="M127" s="64"/>
+      <c r="N127" s="64"/>
+      <c r="O127" s="64"/>
+      <c r="P127" s="64"/>
+      <c r="Q127" s="64"/>
+      <c r="R127" s="64"/>
+      <c r="S127" s="64"/>
+      <c r="T127" s="64"/>
+      <c r="U127" s="65"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="56"/>
+      <c r="A128" s="52"/>
       <c r="B128" s="32" t="s">
         <v>169</v>
       </c>
@@ -16010,7 +16003,7 @@
       <c r="U128" s="17"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="56"/>
+      <c r="A129" s="52"/>
       <c r="B129" s="32" t="s">
         <v>170</v>
       </c>
@@ -16041,7 +16034,7 @@
       <c r="U129" s="17"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="46">
+      <c r="A130" s="51">
         <v>19</v>
       </c>
       <c r="B130" s="34" t="s">
@@ -16074,7 +16067,7 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="46"/>
+      <c r="A131" s="51"/>
       <c r="B131" s="34" t="s">
         <v>172</v>
       </c>
@@ -16105,7 +16098,7 @@
       <c r="U131" s="6"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="46"/>
+      <c r="A132" s="51"/>
       <c r="B132" s="34" t="s">
         <v>173</v>
       </c>
@@ -16136,7 +16129,7 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="46"/>
+      <c r="A133" s="51"/>
       <c r="B133" s="34" t="s">
         <v>174</v>
       </c>
@@ -16167,7 +16160,7 @@
       <c r="U133" s="6"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="46"/>
+      <c r="A134" s="51"/>
       <c r="B134" s="34" t="s">
         <v>175</v>
       </c>
@@ -16198,7 +16191,7 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="46"/>
+      <c r="A135" s="51"/>
       <c r="B135" s="34" t="s">
         <v>176</v>
       </c>
@@ -16229,7 +16222,7 @@
       <c r="U135" s="6"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="46"/>
+      <c r="A136" s="51"/>
       <c r="B136" s="34" t="s">
         <v>177</v>
       </c>
@@ -16275,32 +16268,6 @@
     <row r="150" ht="20.45"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A32:A38"/>
-    <mergeCell ref="D35:U41"/>
-    <mergeCell ref="A39:A45"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="S2:U2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
     <mergeCell ref="A74:A80"/>
     <mergeCell ref="A123:A129"/>
     <mergeCell ref="D127:U127"/>
@@ -16312,6 +16279,32 @@
     <mergeCell ref="A109:A115"/>
     <mergeCell ref="A116:A122"/>
     <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="D29:U31"/>
+    <mergeCell ref="D35:U41"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="S2:U2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
